--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,232 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6548000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6533000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6269000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5748000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5817000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5756000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5497000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5167000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5216000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4985000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4528000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4155000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4120000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3837000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3335000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4009000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4414000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4467000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4113000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3889000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3807000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3898000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3665000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,59 +1298,62 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>308000</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>20000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>211000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>208000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>166000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>34000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>27000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>67000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>45000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>22000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1345,20 +1364,20 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>757000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>29000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>225000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>117000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1366,108 +1385,114 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>15000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>10000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E15" s="3">
         <v>211000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>192000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>191000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>184000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>185000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>189000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>192000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>189000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>188000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>186000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>163000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>150000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>141000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>145000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>144000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>146000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>137000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>122000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>117000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>113000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>111000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>115000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>120000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>115000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>118000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>92000</v>
       </c>
       <c r="AE15" s="3">
         <v>92000</v>
       </c>
       <c r="AF15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3176000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2689000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2613000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2612000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2633000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2644000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2479000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2217000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2389000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2268000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2187000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1958000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2062000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1732000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1628000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1798000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2015000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1812000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1716000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1676000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2573000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1611000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1729000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3372000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3844000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3656000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3136000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3184000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3112000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3018000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2950000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2827000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2717000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2341000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2197000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2058000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2105000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1707000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2211000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2399000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2655000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2397000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2213000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1234000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2287000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1936000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E20" s="3">
         <v>68000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>192000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-151000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>32000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>80000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-106000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-67000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>104000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>209000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>243000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>215000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>84000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-155000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>140000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-58000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>173000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>36000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>28000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>25000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>34000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>21000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>26000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>14000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>11000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3674000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4123000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4040000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3176000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3400000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3377000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3101000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3075000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3120000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3114000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2770000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2460000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2423000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2161000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1936000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2200000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2685000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2734000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2692000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2366000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1375000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2423000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2085000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E22" s="3">
         <v>151000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>144000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>132000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>127000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>120000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>114000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>110000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>108000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>110000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>106000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>107000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>105000</v>
       </c>
       <c r="P22" s="3">
         <v>105000</v>
       </c>
       <c r="Q22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="R22" s="3">
         <v>101000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>69000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>64000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>63000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>51000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>46000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>47000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>48000</v>
       </c>
       <c r="Y22" s="3">
         <v>48000</v>
       </c>
       <c r="Z22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>43000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>41000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>39000</v>
       </c>
       <c r="AD22" s="3">
         <v>39000</v>
       </c>
       <c r="AE22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>30000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3321000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3761000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3704000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2853000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3089000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3072000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2798000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2773000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2823000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2816000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2478000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2190000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2168000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1915000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1690000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1987000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2475000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2534000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2519000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2203000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1215000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2264000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1922000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>530000</v>
+      </c>
+      <c r="E24" s="3">
         <v>563000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>859000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>492000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>564000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>573000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>523000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>142000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>444000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>402000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>412000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>362000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>383000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>402000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>270000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>294000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>402000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>426000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>471000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>341000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>391000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>365000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>353000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>311000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>480000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>502000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>451000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>397000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>378000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2791000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3198000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2845000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2361000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2525000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2499000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2275000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2631000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2379000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2414000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2066000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1828000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1785000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1420000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1693000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2073000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2108000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2048000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1862000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>824000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1899000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1569000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>933000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2791000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3198000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2845000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2361000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2525000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2499000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2275000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2631000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2379000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2414000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2066000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1828000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1785000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1420000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1693000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2073000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2108000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2048000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1862000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>824000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1899000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1569000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>933000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2575,8 +2635,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
@@ -2593,36 +2653,36 @@
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>27000</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>75000</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-68000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-192000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>151000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-32000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-80000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>106000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>67000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-104000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-209000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-243000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-215000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>85000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-84000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>155000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-140000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>58000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-173000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-36000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-28000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>22000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2791000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3198000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2845000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2361000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2525000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2499000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2275000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2631000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2379000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2414000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2066000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1828000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1785000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1420000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1693000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2108000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2048000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1862000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>899000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1899000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1569000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>227000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>933000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2791000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3198000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2845000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2361000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2525000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2499000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2275000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2631000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2379000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2414000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2066000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1828000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1785000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1420000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1693000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2108000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2048000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1862000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>899000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1899000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1569000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>227000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>933000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,284 +3437,294 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8588000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6890000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6170000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6566000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7008000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7633000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5921000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6879000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7421000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6406000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6216000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7246000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10113000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10225000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11137000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10207000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6988000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5101000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5691000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5857000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6682000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6871000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6210000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>592000</v>
+      </c>
+      <c r="E42" s="3">
         <v>602000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>344000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>402000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>400000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>412000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>438000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>449000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>473000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>510000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>544000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>489000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>483000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>400000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>390000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>477000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>688000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>751000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>809000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1317000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1696000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1622000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1535000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5426000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5148000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5249000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4889000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4813000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4264000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4315000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4138000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4459000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3765000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3785000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4398000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4411000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3775000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3971000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3657000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5557000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5274000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4207000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4047000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4728000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3612000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3696000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,468 +3815,486 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4355000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4343000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4767000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4563000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4385000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4514000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4537000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4487000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4596000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4701000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4534000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4272000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4106000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4069000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3883000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3782000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3669000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3721000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3458000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3175000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3065000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2959000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2864000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18961000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16983000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16530000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16420000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16606000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16823000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15211000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15953000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16949000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15382000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15079000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16405000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19113000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18469000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>19381000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18123000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16902000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14847000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14165000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14396000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16171000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15064000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14305000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2899000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2694000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2741000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2705000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2805000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2694000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2745000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2986000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2966000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2658000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2479000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2133000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1970000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1613000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1621000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1509000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1526000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1296000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1276000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>722000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>635000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>480000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>441000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>409000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>427000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>388000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>392000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>298000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>307000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2061000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1972000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2006000</v>
       </c>
       <c r="G48" s="3">
         <v>2006000</v>
       </c>
       <c r="H48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1951000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1950000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1957000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1907000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1860000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1839000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1850000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1902000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1887000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1872000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1901000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1828000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1492000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1348000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1305000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>921000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>876000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>860000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>839000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>829000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>901000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>845000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>748000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>733000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11746000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11510000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11628000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11602000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11381000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10758000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11195000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11300000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11333000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11130000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11274000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10372000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6713000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5666000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5561000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5517000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5438000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5034000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4756000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3969000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3895000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3973000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4017000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6781000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6515000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6119000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6203000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5926000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5386000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5130000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4967000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4514000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4380000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4240000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4040000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3886000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3959000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3692000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3598000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3542000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3312000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3186000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3128000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3238000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2947000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2848000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42448000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39674000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39004000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38936000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38724000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37612000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36231000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37163000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37669000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35410000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34911000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34800000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33584000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31594000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32127000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30648000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29236000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25981000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24731000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23520000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24860000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23340000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22471000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>834000</v>
+      </c>
+      <c r="E57" s="3">
         <v>589000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>643000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>735000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>926000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>615000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>633000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>666000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>738000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>557000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>547000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>476000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>527000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>341000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>369000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>371000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>489000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>505000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>432000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>508000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>537000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>382000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>345000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>370000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>933000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>722000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>654000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>680000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>609000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4809,31 +4942,31 @@
         <v>1337000</v>
       </c>
       <c r="E58" s="3">
+        <v>1337000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1336000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>276000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>274000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>957000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>735000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>778000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>792000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>650000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>649000</v>
       </c>
       <c r="N58" s="3">
         <v>649000</v>
@@ -4841,8 +4974,8 @@
       <c r="O58" s="3">
         <v>649000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
+      <c r="P58" s="3">
+        <v>649000</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
@@ -4850,8 +4983,8 @@
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -4860,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>500000</v>
@@ -4868,8 +5001,8 @@
       <c r="X58" s="3">
         <v>500000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
+      <c r="Y58" s="3">
+        <v>500000</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
@@ -4883,8 +5016,8 @@
       <c r="AC58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -4892,376 +5025,391 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14093000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12593000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12657000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12640000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12971000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11904000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10717000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10484000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11632000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10354000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10101000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10350000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10671000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9617000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9554000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9341000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11415000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10209000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9065000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9238000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10556000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8827000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9110000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16264000</v>
+      </c>
+      <c r="E60" s="3">
         <v>14519000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14636000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13651000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14171000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13476000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12085000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11928000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13162000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11561000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11297000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11475000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11847000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9958000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9923000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9712000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11904000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10714000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9497000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10246000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11593000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9709000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9455000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14344000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14229000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14284000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15292000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13749000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13577000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13746000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13868000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13109000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13211000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13250000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13221000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12023000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12574000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12498000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12466000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8527000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7735000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7806000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5799000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>5858000</v>
       </c>
       <c r="Y61" s="3">
         <v>5858000</v>
       </c>
       <c r="Z61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4843000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4545000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4505000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4586000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4427000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4116000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4138000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4237000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3986000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3836000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3795000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3651000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3197000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3181000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3158000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2972000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2814000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2483000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2319000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2212000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1944000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1906000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1808000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>999000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>982000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>621000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>605000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35519000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33363000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33500000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33606000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32426000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31251000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30060000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30129000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30357000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28707000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28469000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28473000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27193000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25798000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25657000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25250000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23343000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21032000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19723000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18352000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19465000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17565000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17214000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>62564000</v>
+      </c>
+      <c r="E72" s="3">
         <v>60390000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>57730000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>55424000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53607000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>51625000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>49599000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>47800000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>45648000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>43750000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>41771000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40140000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38747000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>37403000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>36288000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>35273000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>33984000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>32289000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>30517000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>28806000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>27283000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>26726000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>25086000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6929000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6311000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5504000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5330000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6298000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6361000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6171000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7034000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7312000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6703000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6442000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6327000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6391000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5796000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6470000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5398000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5893000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4949000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5008000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5168000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5395000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5775000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5257000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2791000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3198000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2845000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2361000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2525000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2499000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2275000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2631000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2379000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2414000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2066000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1828000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1785000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1420000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1693000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2108000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2048000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1862000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>899000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1899000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1569000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>227000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>933000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E83" s="3">
         <v>211000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>192000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>191000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>184000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>185000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>189000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>192000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>189000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>188000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>186000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>163000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>150000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>141000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>145000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>144000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>146000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>137000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>122000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>117000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>113000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>111000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>115000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>120000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>116000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>118000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>92000</v>
       </c>
       <c r="AE83" s="3">
         <v>92000</v>
       </c>
       <c r="AF83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AG83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4130000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3233000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2698000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1919000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3100000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3856000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2457000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1782000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3189000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2543000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2268000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1463000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2253000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1654000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1458000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1859000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2980000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2355000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1536000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1312000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1332000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2367000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1489000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>745000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>992000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-269000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-234000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-233000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-352000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-339000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-277000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-187000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-294000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-228000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-249000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-81000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-65000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-70000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-131000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-116000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-132000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-91000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-83000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-75000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-83000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-90000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-214000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-522000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-218000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-397000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-350000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-308000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-525000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-287000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-438000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-132000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-199000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-119000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-507000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-460000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-626000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-767000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>213000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-269000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-231000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-373000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>367000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,34 +8117,35 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-534000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-538000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-541000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-545000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-473000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-474000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-477000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-434000</v>
       </c>
       <c r="L96" s="3">
         <v>-434000</v>
@@ -7921,64 +8154,67 @@
         <v>-434000</v>
       </c>
       <c r="N96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-439000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-399000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-402000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-401000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-403000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-333000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-335000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-337000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-340000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-259000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-260000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-262000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2350000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-606000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-409000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-582000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-937000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>675000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-86000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>20000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>37000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>284000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-185000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-174000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-28000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-73000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-56000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>77000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-101000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>191000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>115000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>39000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-88000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>59000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-77000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>28000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-54000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-71000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>95000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>71000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>88000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>35000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1723000</v>
+      </c>
+      <c r="E102" s="3">
         <v>221000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-279000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-396000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-580000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1624000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-687000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1061000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>218000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-992000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-898000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>969000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3364000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1997000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-473000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-140000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-752000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-141000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>710000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-656000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>832000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>401000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>440000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,238 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6348000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6548000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6533000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6269000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5748000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5817000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5756000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5497000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5167000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5216000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4985000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4528000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4155000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4120000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3837000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3335000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4009000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4414000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4467000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4113000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3889000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3807000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3898000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,62 +1318,65 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E14" s="3">
         <v>308000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>20000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>211000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>208000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>166000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>34000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>27000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>67000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>45000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>22000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1367,20 +1387,20 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>757000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>29000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>225000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>117000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1388,111 +1408,117 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>15000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>10000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>216000</v>
+      </c>
+      <c r="E15" s="3">
         <v>205000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>211000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>192000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>191000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>184000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>185000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>189000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>192000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>189000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>188000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>186000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>163000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>150000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>141000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>145000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>144000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>146000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>137000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>122000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>117000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>113000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>111000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>115000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>120000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>115000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>118000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>92000</v>
       </c>
       <c r="AF15" s="3">
         <v>92000</v>
       </c>
       <c r="AG15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AH15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2744000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3176000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2689000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2613000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2612000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2633000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2644000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2479000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2217000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2389000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2268000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2187000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1958000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2062000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1732000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1628000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1798000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2015000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1812000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1716000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1676000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2573000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1611000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3604000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3372000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3844000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3656000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3136000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3184000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3112000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3018000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2950000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2827000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2717000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2341000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2197000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2058000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2105000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1707000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2211000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2399000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2655000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2397000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2213000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1234000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2287000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E20" s="3">
         <v>97000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>68000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>192000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-151000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>32000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>80000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-106000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-67000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>104000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>209000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>243000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>215000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-85000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>84000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-155000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>140000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-58000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>173000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>36000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>28000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>25000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>34000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>21000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>26000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>14000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3924000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3674000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4123000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4040000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3176000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3400000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3377000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3101000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3075000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3120000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3114000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2770000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2460000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2423000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2161000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1936000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2200000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2685000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2734000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2692000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2366000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1375000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2423000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E22" s="3">
         <v>148000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>151000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>144000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>132000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>127000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>120000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>114000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>110000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>108000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>110000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>106000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>107000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>105000</v>
       </c>
       <c r="Q22" s="3">
         <v>105000</v>
       </c>
       <c r="R22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="S22" s="3">
         <v>101000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>69000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>64000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>63000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>51000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>46000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>47000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>48000</v>
       </c>
       <c r="Z22" s="3">
         <v>48000</v>
       </c>
       <c r="AA22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>43000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>41000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>39000</v>
       </c>
       <c r="AE22" s="3">
         <v>39000</v>
       </c>
       <c r="AF22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>30000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3558000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3321000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3761000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3704000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2853000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3089000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3072000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2798000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2773000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2823000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2816000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2478000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2190000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2168000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1915000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1690000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1987000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2475000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2534000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2519000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2203000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1215000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2264000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>547000</v>
+      </c>
+      <c r="E24" s="3">
         <v>530000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>563000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>859000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>492000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>564000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>573000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>523000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>142000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>444000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>402000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>412000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>362000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>383000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>402000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>270000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>294000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>402000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>426000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>471000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>341000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>391000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>365000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>353000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>311000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>480000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>502000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>451000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>397000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>378000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3011000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2791000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3198000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2845000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2361000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2525000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2499000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2275000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2631000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2379000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2414000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2066000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1828000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1513000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1420000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1693000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2073000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2108000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2048000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1862000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>824000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1899000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>933000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3011000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2791000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3198000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2845000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2361000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2525000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2499000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2275000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2631000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2379000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2414000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2066000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1828000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1513000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1420000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1693000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2073000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2108000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2048000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1862000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>824000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1899000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>933000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2638,8 +2699,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>5</v>
@@ -2656,36 +2717,36 @@
       <c r="S29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>27000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>75000</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-97000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-68000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-192000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>151000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-32000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-80000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>106000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>67000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-104000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-209000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-243000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-215000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>85000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-84000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>155000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-140000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>58000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-173000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-36000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>22000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3011000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2791000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3198000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2845000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2361000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2525000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2499000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2275000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2631000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2379000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2414000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2066000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1828000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1513000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1420000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1693000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2108000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2048000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1862000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>899000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1899000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>227000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>933000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3011000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2791000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3198000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2845000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2361000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2525000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2499000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2275000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2631000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2379000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2414000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2066000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1828000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1513000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1420000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1693000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2108000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2048000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1862000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>899000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1899000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>227000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>933000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,293 +3524,303 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7293000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8588000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6890000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6170000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6566000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7008000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7633000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5921000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6879000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7421000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6406000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6216000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7246000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10113000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10225000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11137000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10207000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6988000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5101000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5691000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5857000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6682000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6871000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E42" s="3">
         <v>592000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>602000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>344000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>402000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>400000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>412000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>438000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>449000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>473000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>510000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>544000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>489000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>483000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>400000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>390000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>477000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>688000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>751000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>809000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1317000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1696000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1622000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6035000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5426000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5148000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5249000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4889000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4813000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4264000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4315000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4138000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4459000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3765000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3785000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4398000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4411000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3775000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3971000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3657000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5557000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5274000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4207000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4047000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4728000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3612000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,483 +3914,501 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4732000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4355000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4343000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4767000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4563000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4385000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4514000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4537000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4487000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4596000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4701000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4534000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4272000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4106000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4069000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3883000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3782000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3669000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3721000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3458000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3175000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3065000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2959000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18424000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18961000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16983000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16530000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16420000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16606000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16823000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15211000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15953000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16949000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15382000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15079000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16405000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>19113000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18469000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19381000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18123000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16902000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14847000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14165000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14396000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16171000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15064000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2989000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2899000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2694000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2741000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2705000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2805000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2694000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2745000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2986000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2966000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2658000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2479000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2133000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1970000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1613000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1621000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1509000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1526000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1296000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1276000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>722000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>635000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>480000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>441000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>409000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>427000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>388000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>392000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>298000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>307000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2077000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2061000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1972000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2006000</v>
       </c>
       <c r="H48" s="3">
         <v>2006000</v>
       </c>
       <c r="I48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="J48" s="3">
         <v>1951000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1950000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1957000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1907000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1860000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1839000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1850000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1902000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1887000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1872000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1901000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1828000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1492000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1348000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1305000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>921000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>876000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>860000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>839000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>829000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>901000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>845000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>748000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>733000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11668000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11746000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11510000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11628000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11602000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11381000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10758000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11195000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11300000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11333000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11130000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11274000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10372000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6713000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5666000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5561000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5517000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5438000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5034000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4756000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3969000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3895000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3973000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7444000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6781000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6515000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6119000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6203000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5926000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5386000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5130000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4967000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4514000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4380000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4240000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4040000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3886000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3959000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3692000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3598000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3542000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3312000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3186000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3128000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3238000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2947000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42602000</v>
+      </c>
+      <c r="E54" s="3">
         <v>42448000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39674000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>39004000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38936000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38724000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37612000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36231000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37163000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37669000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35410000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34911000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34800000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33584000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31594000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32127000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30648000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29236000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>25981000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24731000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23520000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24860000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23340000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,138 +4968,142 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>790000</v>
+      </c>
+      <c r="E57" s="3">
         <v>834000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>589000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>643000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>735000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>926000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>615000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>633000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>666000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>738000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>557000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>547000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>476000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>527000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>341000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>369000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>371000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>489000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>505000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>432000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>508000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>537000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>382000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>345000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>370000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>933000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>722000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>654000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>680000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>609000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1337000</v>
+        <v>2086000</v>
       </c>
       <c r="E58" s="3">
         <v>1337000</v>
       </c>
       <c r="F58" s="3">
+        <v>1337000</v>
+      </c>
+      <c r="G58" s="3">
         <v>1336000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>276000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>274000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>957000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>735000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>778000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>792000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>650000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>649000</v>
       </c>
       <c r="O58" s="3">
         <v>649000</v>
@@ -4977,8 +5111,8 @@
       <c r="P58" s="3">
         <v>649000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
+      <c r="Q58" s="3">
+        <v>649000</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
@@ -4986,8 +5120,8 @@
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4996,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>500000</v>
@@ -5004,8 +5138,8 @@
       <c r="Y58" s="3">
         <v>500000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
+      <c r="Z58" s="3">
+        <v>500000</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
@@ -5019,8 +5153,8 @@
       <c r="AD58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -5028,388 +5162,403 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14029000</v>
+      </c>
+      <c r="E59" s="3">
         <v>14093000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12593000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12657000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12640000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12971000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11904000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10717000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10484000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11632000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10354000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10101000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10350000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10671000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9617000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9554000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9341000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11415000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10209000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9065000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9238000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10556000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8827000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16905000</v>
+      </c>
+      <c r="E60" s="3">
         <v>16264000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14519000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14636000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13651000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14171000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13476000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12085000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11928000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13162000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11561000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11297000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11475000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11847000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9958000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9923000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9712000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11904000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10714000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9497000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10246000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11593000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9709000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13543000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14344000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14229000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14284000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15292000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13749000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13577000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13746000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13868000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13109000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13211000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13250000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13221000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12023000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12574000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12498000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12466000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8527000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7735000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7806000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5799000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>5858000</v>
       </c>
       <c r="Z61" s="3">
         <v>5858000</v>
       </c>
       <c r="AA61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4846000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4843000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4545000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4505000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4586000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4427000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4116000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4138000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4237000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3986000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3836000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3795000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3651000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3197000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3181000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3158000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2972000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2814000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2483000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2319000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2212000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1944000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1906000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>999000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>982000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>621000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>605000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35359000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35519000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33363000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33500000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33606000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32426000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31251000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30060000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30129000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30357000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28707000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28469000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28473000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27193000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25798000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25657000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25250000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23343000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>21032000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19723000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18352000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19465000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17565000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>64959000</v>
+      </c>
+      <c r="E72" s="3">
         <v>62564000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>60390000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>57730000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55424000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53607000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51625000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>49599000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>47800000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45648000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>43750000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>41771000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40140000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38747000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>37403000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36288000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>35273000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33984000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>32289000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>30517000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>28806000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>27283000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>26726000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7243000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6929000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6311000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5504000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5330000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6298000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6361000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6171000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7034000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7312000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6703000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6442000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6327000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6391000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5796000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6470000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5398000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5893000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4949000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5008000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5168000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5395000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5775000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3011000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2791000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3198000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2845000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2361000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2525000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2499000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2275000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2631000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2379000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2414000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2066000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1828000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1513000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1420000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1693000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2108000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2048000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1862000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>899000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1899000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>227000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>933000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>216000</v>
+      </c>
+      <c r="E83" s="3">
         <v>205000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>211000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>192000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>191000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>184000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>185000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>189000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>192000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>189000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>188000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>186000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>163000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>150000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>141000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>145000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>144000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>146000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>137000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>122000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>117000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>113000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>111000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>115000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>120000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>116000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>118000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>92000</v>
       </c>
       <c r="AF83" s="3">
         <v>92000</v>
       </c>
       <c r="AG83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AH83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1672000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4130000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3233000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2698000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1919000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3100000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3856000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2457000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1782000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3189000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2543000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2268000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1463000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2253000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1654000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1458000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1859000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2980000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2355000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1536000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1312000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1332000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2367000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>745000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>992000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-378000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-269000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-234000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-233000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-352000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-339000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-277000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-187000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-294000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-228000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-249000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-81000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-65000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-79000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-70000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-131000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-116000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-132000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-91000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-83000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-75000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-83000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-214000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-522000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-218000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-397000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-350000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-308000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-525000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-287000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-438000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-132000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-199000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-119000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-507000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-460000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-626000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-767000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>213000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-269000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-231000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>367000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,37 +8351,38 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-616000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-534000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-538000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-541000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-545000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-473000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-474000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-477000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-434000</v>
       </c>
       <c r="M96" s="3">
         <v>-434000</v>
@@ -8157,64 +8391,67 @@
         <v>-434000</v>
       </c>
       <c r="O96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-439000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-399000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-402000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-401000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-403000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-333000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-335000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-337000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-340000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-259000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-260000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2681000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-606000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-409000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2100000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-582000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-937000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>675000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E101" s="3">
         <v>157000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-86000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>20000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>284000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-185000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-174000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-28000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-73000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-56000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>77000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-101000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>191000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>115000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>39000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-88000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>59000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-77000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>28000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-54000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-71000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>95000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>71000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>88000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>35000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1278000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1723000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>221000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-279000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-396000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-580000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1624000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-687000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1061000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>218000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-992000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-898000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>969000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3364000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1997000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-473000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-140000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-752000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-141000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>710000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>832000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>401000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>440000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6961000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6348000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6548000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6533000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6269000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5748000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5817000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5756000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5497000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5167000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5216000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4985000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4528000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4155000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4120000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3837000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3335000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4009000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4414000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4467000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4113000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3889000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3807000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3898000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,65 +1338,68 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E14" s="3">
         <v>126000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>308000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>20000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>211000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>208000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>166000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>34000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>27000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>67000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>45000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>22000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1390,20 +1410,20 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>757000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>29000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>225000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>117000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1411,114 +1431,120 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>15000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>10000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E15" s="3">
         <v>216000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>205000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>211000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>192000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>191000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>184000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>185000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>189000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>192000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>189000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>188000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>186000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>163000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>150000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>141000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>145000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>144000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>146000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>137000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>122000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>117000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>113000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>111000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>115000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>120000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>115000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>118000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>92000</v>
       </c>
       <c r="AG15" s="3">
         <v>92000</v>
       </c>
       <c r="AH15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AI15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2925000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2744000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3176000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2689000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2613000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2612000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2633000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2644000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2479000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2217000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2389000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2268000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2187000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1958000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2062000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1732000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1628000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1798000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2015000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1812000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1716000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1676000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2573000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4036000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3604000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3372000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3844000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3656000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3136000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3184000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3112000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3018000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2950000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2827000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2717000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2341000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2197000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2058000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2105000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1707000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2211000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2399000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2655000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2397000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2213000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2287000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E20" s="3">
         <v>104000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>97000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>68000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>192000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-151000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>32000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>80000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-106000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-67000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>104000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>209000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>243000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>215000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-85000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>84000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-155000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>140000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-58000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>173000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>36000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>28000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>25000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>34000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>21000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>26000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>14000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>11000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4317000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3924000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3674000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4123000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4040000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3176000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3400000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3377000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3101000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3075000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3120000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3114000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2770000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2460000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2423000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2161000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1936000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2200000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2685000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2734000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2692000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2366000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1375000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2423000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E22" s="3">
         <v>150000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>148000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>151000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>144000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>132000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>127000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>120000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>114000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>110000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>108000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>110000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>106000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>107000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>105000</v>
       </c>
       <c r="R22" s="3">
         <v>105000</v>
       </c>
       <c r="S22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="T22" s="3">
         <v>101000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>69000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>64000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>63000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>51000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>46000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>47000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>48000</v>
       </c>
       <c r="AA22" s="3">
         <v>48000</v>
       </c>
       <c r="AB22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>43000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>41000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>39000</v>
       </c>
       <c r="AF22" s="3">
         <v>39000</v>
       </c>
       <c r="AG22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>30000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3939000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3558000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3321000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3761000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3704000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2853000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3089000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3072000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2798000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2773000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2823000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2816000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2478000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2190000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2168000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1915000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1690000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1987000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2475000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2534000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2519000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2203000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1215000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2264000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>681000</v>
+      </c>
+      <c r="E24" s="3">
         <v>547000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>530000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>563000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>859000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>492000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>564000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>573000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>523000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>142000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>444000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>402000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>412000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>362000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>383000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>402000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>270000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>294000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>402000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>426000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>471000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>341000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>391000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>365000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>353000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>311000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>480000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>502000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>451000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>397000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>378000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3011000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2791000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3198000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2845000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2361000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2525000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2499000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2275000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2631000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2379000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2414000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2066000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1828000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1785000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1513000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1420000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1693000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2073000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2108000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2048000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>824000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1899000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>933000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3011000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2791000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3198000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2845000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2361000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2525000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2499000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2275000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2631000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2379000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2414000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2066000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1828000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1785000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1513000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1420000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1693000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2073000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2108000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2048000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>824000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1899000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>933000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2702,8 +2763,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
@@ -2720,36 +2781,36 @@
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>27000</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>75000</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-104000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-97000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-68000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-192000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>151000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-32000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-80000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>106000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>67000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-104000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-209000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-243000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-215000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>85000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-84000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>155000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-140000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>58000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-173000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>22000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3011000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2791000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3198000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2845000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2361000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2525000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2499000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2275000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2631000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2379000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2414000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2066000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1828000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1785000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1513000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1420000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1693000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2108000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2048000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>899000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1899000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>227000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>933000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3011000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2791000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3198000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2845000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2361000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2525000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2499000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2275000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2631000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2379000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2414000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2066000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1828000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1785000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1513000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1420000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1693000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2108000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2048000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>899000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1899000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>227000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>933000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,302 +3611,312 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6996000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7293000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8588000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6890000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6170000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6566000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7008000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7633000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5921000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6879000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7421000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6406000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6216000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7246000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10113000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10225000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11137000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10207000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6988000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5101000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5691000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5857000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6682000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6871000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E42" s="3">
         <v>364000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>592000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>602000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>344000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>402000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>400000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>412000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>438000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>449000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>473000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>510000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>544000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>489000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>483000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>400000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>390000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>477000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>688000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>751000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>809000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1317000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1696000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1622000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5842000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6035000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5426000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5148000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5249000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4889000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4813000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4264000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4315000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4138000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4459000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3765000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3785000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4398000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4411000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3775000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3971000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3657000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5557000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5274000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4207000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4047000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4728000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3612000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4580000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4732000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4355000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4343000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4767000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4563000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4385000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4514000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4537000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4487000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4596000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4701000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4534000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4272000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4106000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4069000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3883000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3782000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3669000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3721000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3458000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3175000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3065000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2959000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17780000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18424000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18961000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16983000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16530000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16420000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16606000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16823000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15211000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15953000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16949000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15382000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15079000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16405000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>19113000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18469000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>19381000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18123000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16902000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14847000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14165000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14396000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16171000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15064000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4122,293 +4227,302 @@
         <v>2989000</v>
       </c>
       <c r="E47" s="3">
+        <v>2989000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2899000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2694000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2741000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2705000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2805000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2694000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2745000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2986000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2966000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2658000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2479000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2133000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1970000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1613000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1621000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1509000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1526000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1296000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1276000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>722000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>635000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>480000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>441000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>409000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>427000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>388000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>392000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>298000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>307000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2148000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2077000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2061000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1972000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2006000</v>
       </c>
       <c r="I48" s="3">
         <v>2006000</v>
       </c>
       <c r="J48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="K48" s="3">
         <v>1951000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1950000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1957000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1907000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1860000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1839000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1850000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1902000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1887000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1872000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1901000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1828000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1492000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1348000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1305000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>921000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>876000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>860000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>839000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>829000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>901000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>845000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>748000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>733000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11712000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11668000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11746000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11510000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11628000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11602000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11381000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10758000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11195000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11300000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11333000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11130000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11274000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10372000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6713000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5666000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5561000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5517000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5438000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5034000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4756000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3969000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3895000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3973000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7704000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7444000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6781000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6515000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6119000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6203000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5926000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5386000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5130000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4967000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4514000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4380000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4240000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4040000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3886000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3959000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3692000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3598000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3542000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3312000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3186000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3128000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3238000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2947000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42333000</v>
+      </c>
+      <c r="E54" s="3">
         <v>42602000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42448000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>39674000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39004000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38936000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38724000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37612000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36231000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37163000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37669000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35410000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34911000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34800000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33584000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31594000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32127000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>30648000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29236000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25981000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24731000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23520000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24860000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23340000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,144 +5099,148 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>835000</v>
+      </c>
+      <c r="E57" s="3">
         <v>790000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>834000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>589000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>643000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>735000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>926000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>615000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>633000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>666000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>738000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>557000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>547000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>476000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>527000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>341000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>369000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>371000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>489000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>505000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>432000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>508000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>537000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>382000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>345000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>370000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>933000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>722000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>654000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>680000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>609000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1086000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2086000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1337000</v>
       </c>
       <c r="F58" s="3">
         <v>1337000</v>
       </c>
       <c r="G58" s="3">
+        <v>1337000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1336000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>276000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>274000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>957000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>735000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>778000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>792000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>650000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>649000</v>
       </c>
       <c r="P58" s="3">
         <v>649000</v>
@@ -5114,8 +5248,8 @@
       <c r="Q58" s="3">
         <v>649000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
+      <c r="R58" s="3">
+        <v>649000</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
@@ -5123,8 +5257,8 @@
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5133,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
         <v>500000</v>
@@ -5141,8 +5275,8 @@
       <c r="Z58" s="3">
         <v>500000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
+      <c r="AA58" s="3">
+        <v>500000</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>5</v>
@@ -5156,8 +5290,8 @@
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -5165,400 +5299,415 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13673000</v>
+      </c>
+      <c r="E59" s="3">
         <v>14029000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14093000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12593000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12657000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12640000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12971000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11904000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10717000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10484000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11632000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10354000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10101000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10350000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10671000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9617000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9554000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9341000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11415000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10209000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9065000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9238000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10556000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8827000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15594000</v>
+      </c>
+      <c r="E60" s="3">
         <v>16905000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16264000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14519000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14636000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13651000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14171000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13476000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12085000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11928000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13162000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11561000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11297000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11475000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11847000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9958000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9923000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9712000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11904000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10714000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9497000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10246000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11593000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9709000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14519000</v>
+      </c>
+      <c r="E61" s="3">
         <v>13543000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14344000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14229000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14284000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15292000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13749000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13577000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13746000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13868000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13109000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13211000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13250000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13221000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12023000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12574000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12498000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12466000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8527000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7735000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7806000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5799000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>5858000</v>
       </c>
       <c r="AA61" s="3">
         <v>5858000</v>
       </c>
       <c r="AB61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4738000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4846000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4843000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4545000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4505000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4586000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4427000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4116000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4138000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4237000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3986000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3836000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3795000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3651000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3197000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3181000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3158000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2972000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2814000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2483000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2319000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2212000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1944000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1906000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>999000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>982000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>621000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>605000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34912000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35359000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35519000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33363000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33500000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33606000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32426000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31251000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30060000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30129000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30357000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28707000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28469000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28473000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27193000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25798000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25657000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25250000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23343000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>21032000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19723000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18352000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19465000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17565000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>67604000</v>
+      </c>
+      <c r="E72" s="3">
         <v>64959000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>62564000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>60390000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>57730000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>55424000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53607000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51625000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49599000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>47800000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45648000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43750000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>41771000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40140000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38747000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37403000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36288000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>35273000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33984000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>32289000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>30517000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>28806000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>27283000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>26726000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7421000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7243000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6929000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6311000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5504000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5330000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6298000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6361000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6171000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7034000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7312000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6703000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6442000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6327000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6391000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5796000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6470000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5398000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5893000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4949000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5008000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5168000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5395000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5775000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3011000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2791000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3198000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2845000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2361000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2525000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2499000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2275000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2631000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2379000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2414000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2066000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1828000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1785000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1513000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1420000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1693000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2108000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2048000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>899000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1899000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>227000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>933000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E83" s="3">
         <v>216000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>205000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>211000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>192000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>191000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>184000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>185000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>189000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>192000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>189000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>188000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>186000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>163000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>150000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>141000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>145000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>144000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>146000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>137000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>122000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>117000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>113000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>111000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>115000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>120000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>116000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>118000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>92000</v>
       </c>
       <c r="AG83" s="3">
         <v>92000</v>
       </c>
       <c r="AH83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AI83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3138000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1672000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4130000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3233000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2698000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1919000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3100000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3856000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2457000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1782000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3189000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2543000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2268000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1463000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2253000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1654000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1458000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1859000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2980000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2355000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1536000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1312000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1332000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2367000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>745000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>992000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-296000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-378000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-269000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-234000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-233000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-352000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-339000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-277000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-187000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-294000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-228000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-249000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-81000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-59000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-79000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-70000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-131000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-116000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-132000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-91000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-83000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-75000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-294000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-174000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-214000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-522000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-218000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-397000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-350000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-308000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-525000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-287000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-438000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-132000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-199000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-119000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-507000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-460000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-626000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-767000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>213000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-269000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>367000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,40 +8585,41 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-615000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-616000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-534000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-538000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-541000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-545000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-473000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-474000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-477000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-434000</v>
       </c>
       <c r="N96" s="3">
         <v>-434000</v>
@@ -8394,64 +8628,67 @@
         <v>-434000</v>
       </c>
       <c r="P96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-439000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-399000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-402000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-401000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-403000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-333000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-335000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-337000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-340000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-259000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3257000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-606000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-409000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2100000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-582000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-937000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>675000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-95000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>157000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-86000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>20000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>37000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>284000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-185000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-174000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-28000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-73000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-56000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>77000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>191000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>115000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>39000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-88000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>59000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-77000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>28000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-54000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-71000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>95000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>71000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>88000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>35000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-385000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1278000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1723000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>221000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-279000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-396000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-580000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1624000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-687000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1061000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>218000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-992000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-898000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>969000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3364000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1997000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-473000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-140000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-752000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-141000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>710000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>832000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>401000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>440000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,252 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7369000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6961000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6348000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6548000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6533000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6269000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5748000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5817000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5756000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5497000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5167000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5216000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4985000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4528000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4155000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4120000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3837000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3335000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4009000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4414000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4467000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4113000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3889000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3807000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3898000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1001,31 +1008,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>7369000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6961000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6348000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6548000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>6533000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>6269000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5748000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,68 +1358,71 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>98000</v>
+        <v>428000</v>
       </c>
       <c r="E14" s="3">
-        <v>126000</v>
+        <v>111000</v>
       </c>
       <c r="F14" s="3">
-        <v>308000</v>
+        <v>120000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>274000</v>
       </c>
       <c r="H14" s="3">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="I14" s="3">
-        <v>211000</v>
+        <v>-103000</v>
       </c>
       <c r="J14" s="3">
+        <v>423000</v>
+      </c>
+      <c r="K14" s="3">
         <v>15000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>208000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>166000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>34000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>27000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>67000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>45000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>22000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
@@ -1413,20 +1433,20 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>757000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>29000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>225000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>117000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1434,16 +1454,19 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>15000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>10000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1451,100 +1474,103 @@
         <v>225000</v>
       </c>
       <c r="E15" s="3">
+        <v>225000</v>
+      </c>
+      <c r="F15" s="3">
         <v>216000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>205000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>211000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>192000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>191000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>184000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>185000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>189000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>192000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>189000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>188000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>186000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>163000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>150000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>141000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>145000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>144000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>146000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>137000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>122000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>117000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>113000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>111000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>115000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>120000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>115000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>118000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>92000</v>
       </c>
       <c r="AH15" s="3">
         <v>92000</v>
       </c>
       <c r="AI15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2925000</v>
+        <v>2999000</v>
       </c>
       <c r="E17" s="3">
-        <v>2744000</v>
+        <v>2827000</v>
       </c>
       <c r="F17" s="3">
-        <v>3176000</v>
+        <v>2618000</v>
       </c>
       <c r="G17" s="3">
+        <v>2869000</v>
+      </c>
+      <c r="H17" s="3">
         <v>2689000</v>
       </c>
-      <c r="H17" s="3">
-        <v>2613000</v>
-      </c>
       <c r="I17" s="3">
-        <v>2612000</v>
+        <v>2593000</v>
       </c>
       <c r="J17" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2633000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2644000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2479000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2217000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2389000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2268000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2187000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1958000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2062000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1732000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1628000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1798000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2015000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1812000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1716000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1676000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2573000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4036000</v>
+        <v>4370000</v>
       </c>
       <c r="E18" s="3">
-        <v>3604000</v>
+        <v>4134000</v>
       </c>
       <c r="F18" s="3">
-        <v>3372000</v>
+        <v>3730000</v>
       </c>
       <c r="G18" s="3">
+        <v>3679000</v>
+      </c>
+      <c r="H18" s="3">
         <v>3844000</v>
       </c>
-      <c r="H18" s="3">
-        <v>3656000</v>
-      </c>
       <c r="I18" s="3">
-        <v>3136000</v>
+        <v>3676000</v>
       </c>
       <c r="J18" s="3">
+        <v>3347000</v>
+      </c>
+      <c r="K18" s="3">
         <v>3184000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3112000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3018000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2950000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2827000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2717000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2341000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2197000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2058000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2105000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1707000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2211000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2399000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2655000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2397000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2213000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1234000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2287000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>56000</v>
+        <v>-7000</v>
       </c>
       <c r="E20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>25000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>32000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>80000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="O20" s="3">
         <v>104000</v>
       </c>
-      <c r="F20" s="3">
-        <v>97000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>68000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>192000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-151000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>32000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>80000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-106000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-67000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>104000</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>209000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>243000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>215000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-85000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>84000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-155000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>140000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-58000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>173000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>36000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>28000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>25000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>34000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>21000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>26000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>14000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>11000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4317000</v>
+        <v>4602000</v>
       </c>
       <c r="E21" s="3">
-        <v>3924000</v>
+        <v>4368000</v>
       </c>
       <c r="F21" s="3">
-        <v>3674000</v>
+        <v>3949000</v>
       </c>
       <c r="G21" s="3">
-        <v>4123000</v>
+        <v>3859000</v>
       </c>
       <c r="H21" s="3">
-        <v>4040000</v>
+        <v>4058000</v>
       </c>
       <c r="I21" s="3">
-        <v>3176000</v>
+        <v>3878000</v>
       </c>
       <c r="J21" s="3">
+        <v>3544000</v>
+      </c>
+      <c r="K21" s="3">
         <v>3400000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3377000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3101000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3075000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3120000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3114000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2770000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2460000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2423000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2161000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1936000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2200000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2685000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2734000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2692000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2366000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1375000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2423000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E22" s="3">
         <v>153000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>150000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>148000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>151000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>144000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>132000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>127000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>120000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>114000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>110000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>108000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>110000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>106000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>107000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>105000</v>
       </c>
       <c r="S22" s="3">
         <v>105000</v>
       </c>
       <c r="T22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="U22" s="3">
         <v>101000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>69000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>64000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>63000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>51000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>46000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>47000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>48000</v>
       </c>
       <c r="AB22" s="3">
         <v>48000</v>
       </c>
       <c r="AC22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>43000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>41000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>39000</v>
       </c>
       <c r="AG22" s="3">
         <v>39000</v>
       </c>
       <c r="AH22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>30000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3866000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3939000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3558000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3321000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3761000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3704000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2853000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3089000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3072000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2798000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2773000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2823000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2816000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2478000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2190000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2168000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1915000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1690000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1987000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2475000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2534000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2519000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2203000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2264000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>603000</v>
+      </c>
+      <c r="E24" s="3">
         <v>681000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>547000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>530000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>563000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>859000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>492000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>564000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>573000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>523000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>142000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>444000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>402000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>412000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>362000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>383000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>402000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>270000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>294000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>402000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>426000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>471000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>341000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>391000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>365000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>353000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>311000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>480000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>502000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>451000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>397000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>378000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3258000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3011000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2791000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3198000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2845000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2361000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2525000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2499000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2275000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2631000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2379000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2414000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2066000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1828000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1785000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1513000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1420000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1693000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2073000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2108000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2048000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1862000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>824000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1899000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>933000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3258000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3011000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2791000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3198000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2845000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2361000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2525000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2499000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2275000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2631000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2379000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2414000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2066000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1828000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1785000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1513000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1420000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1693000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2073000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2108000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2048000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1862000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>824000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1899000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>933000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2766,8 +2827,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>5</v>
@@ -2784,36 +2845,36 @@
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>27000</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>75000</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-56000</v>
+        <v>7000</v>
       </c>
       <c r="E32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>106000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>67000</v>
+      </c>
+      <c r="O32" s="3">
         <v>-104000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-97000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-68000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-192000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>151000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-80000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>106000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>67000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-104000</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-209000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-243000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-215000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>85000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-84000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>155000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-140000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>58000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-173000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>22000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3258000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3011000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2791000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3198000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2845000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2361000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2525000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2499000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2275000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2631000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2379000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2414000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2066000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1828000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1785000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1513000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1420000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1693000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2108000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2048000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1862000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>899000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1899000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>227000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>933000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3258000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3011000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2791000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3198000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2845000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2361000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2525000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2499000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2275000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2631000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2379000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2414000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2066000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1828000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1785000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1513000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1420000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1693000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2108000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2048000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1862000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>899000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1899000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>227000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>933000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,334 +3698,344 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11063000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6996000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7293000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8588000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6890000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6170000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6566000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7008000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7633000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5921000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6879000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7421000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6406000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6216000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7246000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10113000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10225000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11137000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10207000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6988000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5101000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5691000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5857000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6682000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6871000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E42" s="3">
         <v>362000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>364000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>592000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>602000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>344000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>402000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>400000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>412000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>438000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>449000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>473000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>510000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>544000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>489000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>483000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>400000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>390000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>477000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>688000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>751000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>809000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1317000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1696000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1622000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5842000</v>
+        <v>4014000</v>
       </c>
       <c r="E43" s="3">
-        <v>6035000</v>
+        <v>4195000</v>
       </c>
       <c r="F43" s="3">
-        <v>5426000</v>
+        <v>4231000</v>
       </c>
       <c r="G43" s="3">
-        <v>5148000</v>
+        <v>4060000</v>
       </c>
       <c r="H43" s="3">
-        <v>5249000</v>
+        <v>3925000</v>
       </c>
       <c r="I43" s="3">
-        <v>4889000</v>
+        <v>3763000</v>
       </c>
       <c r="J43" s="3">
+        <v>3511000</v>
+      </c>
+      <c r="K43" s="3">
         <v>4813000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4264000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4315000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4138000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4459000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3765000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3785000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4398000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4411000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3775000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3971000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3657000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5557000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5274000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4207000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4047000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4728000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3612000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,513 +4112,531 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4580000</v>
+        <v>6885000</v>
       </c>
       <c r="E45" s="3">
-        <v>4732000</v>
+        <v>6227000</v>
       </c>
       <c r="F45" s="3">
-        <v>4355000</v>
+        <v>6536000</v>
       </c>
       <c r="G45" s="3">
-        <v>4343000</v>
+        <v>5721000</v>
       </c>
       <c r="H45" s="3">
-        <v>4767000</v>
+        <v>5566000</v>
       </c>
       <c r="I45" s="3">
-        <v>4563000</v>
+        <v>5655000</v>
       </c>
       <c r="J45" s="3">
+        <v>5345000</v>
+      </c>
+      <c r="K45" s="3">
         <v>4385000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4514000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4537000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4487000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4596000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4701000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4534000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4272000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4106000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4069000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3883000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3782000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3669000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3721000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3458000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3175000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3065000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2959000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22300000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17780000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18424000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18961000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16983000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16530000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16420000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16606000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16823000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15211000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15953000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16949000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15382000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15079000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16405000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19113000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18469000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19381000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18123000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16902000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14847000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14165000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14396000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16171000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15064000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2989000</v>
+        <v>1601000</v>
       </c>
       <c r="E47" s="3">
-        <v>2989000</v>
+        <v>1709000</v>
       </c>
       <c r="F47" s="3">
-        <v>2899000</v>
+        <v>1737000</v>
       </c>
       <c r="G47" s="3">
+        <v>1729000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1650000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1664000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1503000</v>
+      </c>
+      <c r="K47" s="3">
+        <v>2805000</v>
+      </c>
+      <c r="L47" s="3">
         <v>2694000</v>
       </c>
-      <c r="H47" s="3">
-        <v>2741000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2705000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>2805000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>2694000</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2745000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2986000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2966000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2658000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2479000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2133000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1970000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1613000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1621000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1509000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1526000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1296000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1276000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>722000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>635000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>480000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>441000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>409000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>427000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>388000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>392000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>298000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>307000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2176000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2148000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2077000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2061000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1972000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2006000</v>
       </c>
       <c r="J48" s="3">
         <v>2006000</v>
       </c>
       <c r="K48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="L48" s="3">
         <v>1951000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1950000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1957000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1907000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1860000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1839000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1850000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1902000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1887000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1872000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1901000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1828000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1492000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1348000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1305000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>921000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>876000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>860000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>839000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>829000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>901000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>845000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>748000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>733000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11956000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11712000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11668000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11746000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11510000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11628000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11602000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11381000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10758000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11195000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11300000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11333000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11130000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11274000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10372000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6713000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5666000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5561000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5517000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5438000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5034000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4756000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3969000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3895000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3973000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7704000</v>
+        <v>1560000</v>
       </c>
       <c r="E52" s="3">
-        <v>7444000</v>
+        <v>1602000</v>
       </c>
       <c r="F52" s="3">
-        <v>6781000</v>
+        <v>1473000</v>
       </c>
       <c r="G52" s="3">
-        <v>6515000</v>
+        <v>1426000</v>
       </c>
       <c r="H52" s="3">
-        <v>6119000</v>
+        <v>1272000</v>
       </c>
       <c r="I52" s="3">
-        <v>6203000</v>
+        <v>1297000</v>
       </c>
       <c r="J52" s="3">
+        <v>1423000</v>
+      </c>
+      <c r="K52" s="3">
         <v>5926000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5386000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5130000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4967000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4514000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4380000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4240000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4040000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3886000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3959000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3692000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3598000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3542000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3312000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3186000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3128000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3238000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2947000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47237000</v>
+      </c>
+      <c r="E54" s="3">
         <v>42333000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42602000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42448000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39674000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39004000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38936000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38724000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37612000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36231000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37163000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37669000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35410000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34911000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34800000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33584000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31594000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32127000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>30648000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29236000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>25981000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24731000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23520000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24860000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23340000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,150 +5230,154 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>911000</v>
+      </c>
+      <c r="E57" s="3">
         <v>835000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>790000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>834000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>589000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>643000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>735000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>926000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>615000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>633000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>666000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>738000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>557000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>547000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>476000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>527000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>341000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>369000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>371000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>489000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>505000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>432000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>508000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>537000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>382000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>345000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>370000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>933000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>722000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>654000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>680000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>609000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1086000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2086000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>1479000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1337000</v>
       </c>
-      <c r="G58" s="3">
-        <v>1337000</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1336000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>276000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>274000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>957000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>735000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>778000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>792000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>650000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>649000</v>
       </c>
       <c r="Q58" s="3">
         <v>649000</v>
@@ -5251,8 +5385,8 @@
       <c r="R58" s="3">
         <v>649000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
+      <c r="S58" s="3">
+        <v>649000</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
@@ -5260,8 +5394,8 @@
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5270,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>500000</v>
@@ -5278,8 +5412,8 @@
       <c r="AA58" s="3">
         <v>500000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
+      <c r="AB58" s="3">
+        <v>500000</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>5</v>
@@ -5293,8 +5427,8 @@
       <c r="AF58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5302,412 +5436,427 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13673000</v>
+        <v>6882000</v>
       </c>
       <c r="E59" s="3">
-        <v>14029000</v>
+        <v>5979000</v>
       </c>
       <c r="F59" s="3">
-        <v>14093000</v>
+        <v>6609000</v>
       </c>
       <c r="G59" s="3">
-        <v>12593000</v>
+        <v>5917000</v>
       </c>
       <c r="H59" s="3">
-        <v>12657000</v>
+        <v>5373000</v>
       </c>
       <c r="I59" s="3">
-        <v>12640000</v>
+        <v>5989000</v>
       </c>
       <c r="J59" s="3">
+        <v>5918000</v>
+      </c>
+      <c r="K59" s="3">
         <v>12971000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11904000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10717000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10484000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11632000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10354000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10101000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10350000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10671000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9617000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9554000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9341000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11415000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10209000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9065000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9238000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10556000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8827000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17294000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15594000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16905000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16264000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14519000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14636000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13651000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14171000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13476000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12085000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11928000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13162000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11561000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11297000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11475000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11847000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9958000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9923000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9712000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11904000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10714000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9497000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10246000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11593000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9709000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17608000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14519000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13543000</v>
       </c>
-      <c r="F61" s="3">
-        <v>14344000</v>
-      </c>
       <c r="G61" s="3">
+        <v>14977000</v>
+      </c>
+      <c r="H61" s="3">
         <v>14229000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14284000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15292000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13749000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13577000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13746000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13868000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13109000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13211000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13250000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13221000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12023000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12574000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12498000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12466000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8527000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7735000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7806000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5799000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>5858000</v>
       </c>
       <c r="AB61" s="3">
         <v>5858000</v>
       </c>
       <c r="AC61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4738000</v>
+        <v>4102000</v>
       </c>
       <c r="E62" s="3">
-        <v>4846000</v>
+        <v>4068000</v>
       </c>
       <c r="F62" s="3">
-        <v>4843000</v>
+        <v>4155000</v>
       </c>
       <c r="G62" s="3">
-        <v>4545000</v>
+        <v>3471000</v>
       </c>
       <c r="H62" s="3">
-        <v>4505000</v>
+        <v>3860000</v>
       </c>
       <c r="I62" s="3">
-        <v>4586000</v>
+        <v>3820000</v>
       </c>
       <c r="J62" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="K62" s="3">
         <v>4427000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4116000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4138000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4237000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3986000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3836000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3795000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3651000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3197000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3181000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3158000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2972000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2814000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2483000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2319000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2212000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1944000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1906000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>999000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>982000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>621000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>605000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>34912000</v>
+        <v>39739000</v>
       </c>
       <c r="E66" s="3">
-        <v>35359000</v>
+        <v>34851000</v>
       </c>
       <c r="F66" s="3">
-        <v>35519000</v>
+        <v>35294000</v>
       </c>
       <c r="G66" s="3">
-        <v>33363000</v>
+        <v>35451000</v>
       </c>
       <c r="H66" s="3">
-        <v>33500000</v>
+        <v>33293000</v>
       </c>
       <c r="I66" s="3">
-        <v>33606000</v>
+        <v>33425000</v>
       </c>
       <c r="J66" s="3">
+        <v>33529000</v>
+      </c>
+      <c r="K66" s="3">
         <v>32426000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31251000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30060000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30129000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30357000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28707000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28469000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28473000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>27193000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25798000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25657000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25250000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23343000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>21032000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19723000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18352000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19465000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17565000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>70258000</v>
+      </c>
+      <c r="E72" s="3">
         <v>67604000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>64959000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>62564000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>60390000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57730000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>55424000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>53607000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51625000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49599000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>47800000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>45648000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43750000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>41771000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>40140000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38747000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>37403000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>36288000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>35273000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33984000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>32289000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>30517000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>28806000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>27283000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>26726000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7440000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7421000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7243000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6929000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6311000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5504000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5330000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6298000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6361000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6171000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7034000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7312000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6703000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6442000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6327000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6391000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5796000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6470000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5398000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5893000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4949000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5008000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5168000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5395000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5775000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3258000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3011000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2791000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3198000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2845000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2361000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2525000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2499000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2275000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2631000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2379000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2414000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2066000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1828000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1785000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1513000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1420000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1693000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2108000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2048000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1862000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>899000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1899000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>227000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>933000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>225000</v>
+        <v>211000</v>
       </c>
       <c r="E83" s="3">
-        <v>216000</v>
+        <v>192000</v>
       </c>
       <c r="F83" s="3">
-        <v>205000</v>
+        <v>191000</v>
       </c>
       <c r="G83" s="3">
-        <v>211000</v>
+        <v>321000</v>
       </c>
       <c r="H83" s="3">
+        <v>185000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>189000</v>
+      </c>
+      <c r="J83" s="3">
         <v>192000</v>
       </c>
-      <c r="I83" s="3">
-        <v>191000</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>184000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>185000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>189000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>192000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>189000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>188000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>186000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>163000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>150000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>141000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>145000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>144000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>146000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>137000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>122000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>117000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>113000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>111000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>115000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>120000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>116000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>118000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>92000</v>
       </c>
       <c r="AH83" s="3">
         <v>92000</v>
       </c>
       <c r="AI83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5136000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3138000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1672000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4130000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3233000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2698000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1919000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3100000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3856000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2457000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1782000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3189000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2543000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2268000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1463000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2253000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1654000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1458000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1859000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2980000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2355000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1536000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1312000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1332000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2367000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>745000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>992000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-296000</v>
+        <v>-107000</v>
       </c>
       <c r="E91" s="3">
-        <v>-378000</v>
+        <v>-115000</v>
       </c>
       <c r="F91" s="3">
-        <v>-269000</v>
+        <v>-157000</v>
       </c>
       <c r="G91" s="3">
-        <v>-234000</v>
+        <v>-77000</v>
       </c>
       <c r="H91" s="3">
-        <v>-233000</v>
+        <v>-104000</v>
       </c>
       <c r="I91" s="3">
-        <v>-352000</v>
+        <v>-80000</v>
       </c>
       <c r="J91" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-339000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-277000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-187000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-294000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-228000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-249000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-65000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-59000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-79000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-70000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-131000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-116000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-132000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-83000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-294000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-174000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-214000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-522000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-218000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-397000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-350000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-308000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-525000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-287000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-438000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-132000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-199000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-119000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-507000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-460000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-626000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-767000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>213000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>367000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,43 +8819,44 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-615000</v>
+        <v>611000</v>
       </c>
       <c r="E96" s="3">
-        <v>-616000</v>
+        <v>615000</v>
       </c>
       <c r="F96" s="3">
-        <v>-534000</v>
+        <v>616000</v>
       </c>
       <c r="G96" s="3">
-        <v>-538000</v>
+        <v>534000</v>
       </c>
       <c r="H96" s="3">
-        <v>-541000</v>
+        <v>538000</v>
       </c>
       <c r="I96" s="3">
-        <v>-545000</v>
+        <v>541000</v>
       </c>
       <c r="J96" s="3">
+        <v>545000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-473000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-474000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-477000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-434000</v>
       </c>
       <c r="O96" s="3">
         <v>-434000</v>
@@ -8631,64 +8865,67 @@
         <v>-434000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-439000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-399000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-402000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-401000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-403000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-333000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-335000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-337000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-340000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-259000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-857000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3257000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-606000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-409000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2100000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-582000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-937000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>675000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>37000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>284000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>284000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>77000</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>191000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>115000</v>
+      </c>
+      <c r="U101" s="3">
+        <v>39000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>59000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="Y101" s="3">
         <v>28000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-95000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>157000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-86000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>37000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>284000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-185000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-73000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-56000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>77000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-101000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>191000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>115000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>39000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-88000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>59000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>28000</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-54000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>95000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>71000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>88000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>35000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4165000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-385000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1278000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1723000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>221000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-279000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-396000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-580000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1624000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-687000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1061000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>218000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-992000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-898000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>969000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3364000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1997000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-473000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-140000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-752000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>710000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>832000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>401000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>440000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,259 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7489000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7369000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6961000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6348000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6548000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6533000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6269000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5748000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5817000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5756000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5497000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5167000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5216000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4985000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4528000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4155000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4120000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3837000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3335000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4009000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4414000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4467000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4113000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3889000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3807000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3898000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1011,35 +1017,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7489000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7369000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6961000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6348000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6548000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6533000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6269000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5748000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,71 +1377,74 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E14" s="3">
         <v>428000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>111000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>120000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>274000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-103000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>423000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>208000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>166000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>34000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>27000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>67000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>45000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>22000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1436,20 +1455,20 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>757000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>29000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>225000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>117000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1457,120 +1476,126 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>15000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>225000</v>
+        <v>231000</v>
       </c>
       <c r="E15" s="3">
         <v>225000</v>
       </c>
       <c r="F15" s="3">
+        <v>225000</v>
+      </c>
+      <c r="G15" s="3">
         <v>216000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>205000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>211000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>192000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>191000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>184000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>185000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>189000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>192000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>189000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>188000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>186000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>163000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>150000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>141000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>145000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>144000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>146000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>137000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>122000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>117000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>113000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>111000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>115000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>120000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>115000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>118000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>92000</v>
       </c>
       <c r="AI15" s="3">
         <v>92000</v>
       </c>
       <c r="AJ15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AK15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2999000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2827000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2618000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2869000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2868000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2689000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2593000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2401000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2633000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2644000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2479000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2217000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2389000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2268000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2187000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1958000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2062000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1732000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1628000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1798000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2015000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1812000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1716000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1676000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2573000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4218000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4370000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4134000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3730000</v>
       </c>
-      <c r="G18" s="3">
-        <v>3679000</v>
-      </c>
       <c r="H18" s="3">
+        <v>3680000</v>
+      </c>
+      <c r="I18" s="3">
         <v>3844000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3676000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3347000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3184000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3112000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3018000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2950000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2827000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2717000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2341000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2197000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2058000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2105000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1707000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2211000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2399000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2655000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2397000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2213000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1234000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2287000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>32000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>80000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>104000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>209000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>243000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>100000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>215000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>84000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-155000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>140000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>173000</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>36000</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>25000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>32000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>80000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-106000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-67000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>104000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>209000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>243000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>215000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-85000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>84000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-155000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>140000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-58000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>173000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>36000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>28000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>25000</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>34000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>21000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>26000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>14000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>11000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4450000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4602000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4368000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3949000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3859000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4058000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3878000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3544000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3400000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3377000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3101000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3075000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3120000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3114000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2770000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2460000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2423000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2161000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1936000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2200000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2685000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2734000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2692000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2366000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1375000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2423000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E22" s="3">
         <v>159000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>153000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>150000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>148000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>151000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>144000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>132000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>127000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>120000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>114000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>110000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>108000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>110000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>106000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>107000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>105000</v>
       </c>
       <c r="T22" s="3">
         <v>105000</v>
       </c>
       <c r="U22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="V22" s="3">
         <v>101000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>69000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>64000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>63000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>51000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>46000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>47000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>48000</v>
       </c>
       <c r="AC22" s="3">
         <v>48000</v>
       </c>
       <c r="AD22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>43000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>41000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>39000</v>
       </c>
       <c r="AH22" s="3">
         <v>39000</v>
       </c>
       <c r="AI22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3891000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3866000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3939000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3558000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3321000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3761000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3704000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2853000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3089000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3072000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2798000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2773000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2823000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2816000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2478000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2190000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2168000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1915000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1690000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1987000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2475000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2534000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2519000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2203000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2264000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>549000</v>
+      </c>
+      <c r="E24" s="3">
         <v>603000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>681000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>547000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>530000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>563000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>859000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>492000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>564000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>573000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>523000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>142000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>444000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>402000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>412000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>362000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>383000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>402000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>270000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>294000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>402000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>426000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>471000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>341000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>391000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>365000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>353000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>311000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>480000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>502000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>451000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>397000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>378000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3342000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3263000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3258000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3011000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2791000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3198000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2845000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2361000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2525000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2499000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2275000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2631000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2379000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2414000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2066000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1828000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1785000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1513000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1420000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1693000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2073000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2108000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2048000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1862000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>824000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1899000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>933000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3342000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3263000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3258000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3011000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2791000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3198000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2845000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2361000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2525000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2499000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2275000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2631000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2379000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2414000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2066000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1828000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1785000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1513000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1420000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1693000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2073000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2108000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2048000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1862000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>824000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1899000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>933000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2830,8 +2890,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -2848,36 +2908,36 @@
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>27000</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>75000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>7000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>106000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>67000</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-209000</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-243000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-215000</v>
+      </c>
+      <c r="U32" s="3">
+        <v>85000</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="W32" s="3">
+        <v>155000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>58000</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-173000</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-25000</v>
       </c>
-      <c r="H32" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-80000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>106000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>67000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-104000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-209000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-243000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-215000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>85000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-84000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>155000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-140000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>58000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-173000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-36000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3342000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3263000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3258000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3011000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2791000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3198000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2845000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2361000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2525000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2499000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2275000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2631000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2379000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2414000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2066000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1828000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1785000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1513000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1420000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1693000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2100000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2108000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2048000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1862000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>899000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1899000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>227000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>933000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3342000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3263000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3258000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3011000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2791000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3198000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2845000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2361000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2525000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2499000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2275000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2631000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2379000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2414000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2066000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1828000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1785000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1513000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1420000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1693000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2100000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2108000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2048000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1862000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>899000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1899000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>227000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>933000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,320 +3784,330 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8442000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11063000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6996000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7293000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8588000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6890000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6170000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6566000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7008000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7633000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5921000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6879000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7421000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6406000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6216000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7246000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10113000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10225000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11137000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10207000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6988000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5101000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5691000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5857000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6682000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6871000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E42" s="3">
         <v>338000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>362000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>364000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>592000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>602000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>344000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>402000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>400000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>412000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>438000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>449000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>473000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>510000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>544000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>489000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>483000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>400000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>390000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>477000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>688000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>751000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>809000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1317000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1696000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1622000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3773000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4014000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4195000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4231000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4060000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3925000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3763000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3511000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4813000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4264000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4315000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4138000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4459000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3765000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3785000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4398000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4411000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3775000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3971000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3657000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5557000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5274000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4207000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4047000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4728000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3612000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,528 +4210,546 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6687000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6885000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6227000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6536000</v>
       </c>
-      <c r="G45" s="3">
-        <v>5721000</v>
-      </c>
       <c r="H45" s="3">
+        <v>5689000</v>
+      </c>
+      <c r="I45" s="3">
         <v>5566000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5655000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5345000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4385000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4514000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4537000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4487000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4596000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4701000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4534000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4272000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4106000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4069000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3883000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3782000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3669000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3721000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3458000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3175000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3065000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2959000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19724000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22300000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17780000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18424000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18961000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16983000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16530000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16420000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16606000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16823000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15211000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15953000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16949000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15382000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15079000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16405000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>19113000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18469000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19381000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18123000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16902000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14847000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14165000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14396000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16171000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15064000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1607000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1601000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1709000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1737000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1729000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1650000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1664000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1503000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2805000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2694000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2745000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2986000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2966000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2658000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2479000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2133000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1970000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1613000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1621000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1509000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1526000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1296000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1276000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>722000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>635000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>480000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>441000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>409000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>427000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>388000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>392000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>298000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>307000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2138000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2176000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2148000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2077000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2061000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1972000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2006000</v>
       </c>
       <c r="K48" s="3">
         <v>2006000</v>
       </c>
       <c r="L48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="M48" s="3">
         <v>1951000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1950000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1957000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1907000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1860000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1839000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1850000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1902000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1887000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1872000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1901000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1828000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1492000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1348000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1305000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>921000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>876000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>860000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>839000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>829000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>901000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>845000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>748000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>733000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14646000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11956000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11712000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11668000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11746000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11510000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11628000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11602000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11381000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10758000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11195000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11300000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11333000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11130000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11274000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10372000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6713000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5666000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5561000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5517000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5438000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5034000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4756000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3969000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3895000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3973000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1560000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1602000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1473000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1426000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1272000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1297000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1423000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5926000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5386000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5130000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4967000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4514000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4380000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4240000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4040000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3886000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3959000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3692000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3598000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3542000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3312000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3186000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3128000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3238000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2947000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48081000</v>
+      </c>
+      <c r="E54" s="3">
         <v>47237000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42333000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42602000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42448000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39674000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>39004000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38936000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38724000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37612000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36231000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37163000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37669000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35410000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34911000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34800000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33584000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31594000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32127000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>30648000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29236000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>25981000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24731000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23520000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24860000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23340000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,156 +5360,160 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>929000</v>
+      </c>
+      <c r="E57" s="3">
         <v>911000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>835000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>790000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>834000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>589000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>643000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>735000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>926000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>615000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>633000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>666000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>738000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>557000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>547000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>476000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>527000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>341000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>369000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>371000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>489000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>505000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>432000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>508000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>537000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>382000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>345000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>370000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>933000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>722000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>654000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>680000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>609000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>883000</v>
+      </c>
+      <c r="E58" s="3">
         <v>750000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1086000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2086000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1479000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1337000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1336000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>276000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>274000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>957000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>735000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>778000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>792000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>650000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>649000</v>
       </c>
       <c r="R58" s="3">
         <v>649000</v>
@@ -5388,8 +5521,8 @@
       <c r="S58" s="3">
         <v>649000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
+      <c r="T58" s="3">
+        <v>649000</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
@@ -5397,8 +5530,8 @@
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5407,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>500000</v>
@@ -5415,8 +5548,8 @@
       <c r="AB58" s="3">
         <v>500000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
+      <c r="AC58" s="3">
+        <v>500000</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>5</v>
@@ -5430,8 +5563,8 @@
       <c r="AG58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
@@ -5439,424 +5572,439 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7469000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6882000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5979000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6609000</v>
       </c>
-      <c r="G59" s="3">
-        <v>5917000</v>
-      </c>
       <c r="H59" s="3">
+        <v>5920000</v>
+      </c>
+      <c r="I59" s="3">
         <v>5373000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5989000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5918000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12971000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11904000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10717000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10484000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11632000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10354000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10101000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10350000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10671000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9617000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9554000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9341000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11415000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10209000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9065000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9238000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10556000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8827000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19220000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17294000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15594000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16905000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16264000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14519000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14636000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13651000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14171000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13476000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12085000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11928000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13162000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11561000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11297000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11475000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11847000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9958000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9923000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9712000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11904000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10714000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9497000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10246000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11593000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9709000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18103000</v>
+      </c>
+      <c r="E61" s="3">
         <v>17608000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14519000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13543000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14977000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14229000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14284000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15292000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13749000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13577000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13746000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13868000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13109000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13211000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13250000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13221000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12023000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12574000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12498000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12466000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8527000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7735000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7806000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5799000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>5858000</v>
       </c>
       <c r="AC61" s="3">
         <v>5858000</v>
       </c>
       <c r="AD61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3477000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4102000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4068000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4155000</v>
       </c>
-      <c r="G62" s="3">
-        <v>3471000</v>
-      </c>
       <c r="H62" s="3">
+        <v>3523000</v>
+      </c>
+      <c r="I62" s="3">
         <v>3860000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3820000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3931000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4427000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4116000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4138000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4237000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3986000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3836000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3795000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3651000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3197000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3181000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3158000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2972000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2814000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2483000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2319000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2212000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1944000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1906000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>999000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>982000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>621000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>605000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41566000</v>
+      </c>
+      <c r="E66" s="3">
         <v>39739000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34851000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35294000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35451000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33293000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33425000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33529000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32426000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31251000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30060000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30129000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30357000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28707000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28469000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28473000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27193000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25798000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25657000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25250000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23343000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21032000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19723000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18352000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19465000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17565000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>72907000</v>
+      </c>
+      <c r="E72" s="3">
         <v>70258000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>67604000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>64959000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>62564000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>60390000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57730000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>55424000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>53607000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51625000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49599000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>47800000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>45648000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>43750000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41771000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>40140000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38747000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37403000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36288000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>35273000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33984000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>32289000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>30517000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>28806000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>27283000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>26726000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6485000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7440000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7421000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7243000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6929000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6311000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5504000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5330000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6298000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6361000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6171000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7034000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7312000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6703000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6442000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6327000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6391000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5796000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6470000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5398000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5893000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4949000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5008000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5168000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5395000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5775000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3342000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3263000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3258000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3011000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2791000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3198000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2845000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2361000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2525000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2499000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2275000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2631000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2379000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2414000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2066000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1828000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1785000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1513000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1420000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1693000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2100000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2108000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2048000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1862000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>899000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1899000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>227000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>933000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E83" s="3">
         <v>211000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>192000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>191000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>321000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>185000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>189000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>192000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>184000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>185000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>189000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>192000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>189000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>188000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>186000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>163000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>150000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>141000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>145000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>144000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>146000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>137000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>122000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>117000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>113000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>111000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>115000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>120000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>116000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>118000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>92000</v>
       </c>
       <c r="AI83" s="3">
         <v>92000</v>
       </c>
       <c r="AJ83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AK83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4834000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5136000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3138000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1672000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4130000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3233000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2698000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1919000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3100000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3856000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2457000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1782000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3189000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2543000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2268000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1463000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2253000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1654000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1458000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1859000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2980000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2355000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1536000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1332000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2367000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>745000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>992000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-107000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-115000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-157000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-104000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-80000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-110000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-339000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-277000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-187000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-294000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-228000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-249000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-81000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-65000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-59000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-79000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-70000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-131000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-116000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-132000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-91000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2678000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-256000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-294000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-174000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-214000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-522000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-218000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-397000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-350000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-308000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-525000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-287000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-438000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-199000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-119000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-507000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-460000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-626000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-767000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>213000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>367000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,46 +9052,47 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E96" s="3">
         <v>611000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>615000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>616000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>534000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>538000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>541000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>545000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-473000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-474000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-477000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-434000</v>
       </c>
       <c r="P96" s="3">
         <v>-434000</v>
@@ -8868,64 +9101,67 @@
         <v>-434000</v>
       </c>
       <c r="R96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-439000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-399000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-402000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-401000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-403000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-333000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-335000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-337000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-259000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4041000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-857000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3257000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-606000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-409000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2100000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-582000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-937000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>675000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-86000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>20000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>37000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>284000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-185000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-174000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-28000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>284000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-185000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-174000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-73000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>77000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-101000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>191000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>115000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>39000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-88000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>59000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-77000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>28000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-54000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-71000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>95000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>71000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>88000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>35000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2159000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4165000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-385000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1278000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1723000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>221000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-279000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-396000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-580000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1624000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-687000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1061000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>218000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-992000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-898000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>969000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3364000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1997000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-473000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-140000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-752000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>710000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>832000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>401000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>440000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,265 +656,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7250000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7489000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7369000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6961000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6348000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6548000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6533000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6269000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5748000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5817000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5756000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5497000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5167000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5216000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4985000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4528000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4155000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4120000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3837000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3335000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4009000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4414000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4467000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4113000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3889000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3807000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3898000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1020,38 +1027,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7250000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7489000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7369000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6961000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6348000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6548000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6533000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6269000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5748000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,74 +1397,77 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E14" s="3">
         <v>240000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>428000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>111000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>120000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>274000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-103000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>423000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>208000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>166000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>34000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>27000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>67000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>45000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>22000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1458,20 +1478,20 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>757000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>29000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>225000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>117000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1479,123 +1499,129 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>10000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E15" s="3">
         <v>231000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>225000</v>
       </c>
       <c r="F15" s="3">
         <v>225000</v>
       </c>
       <c r="G15" s="3">
+        <v>225000</v>
+      </c>
+      <c r="H15" s="3">
         <v>216000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>205000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>211000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>192000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>191000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>184000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>185000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>189000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>192000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>189000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>188000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>186000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>163000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>150000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>141000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>145000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>144000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>146000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>137000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>122000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>117000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>113000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>111000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>115000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>120000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>115000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>118000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>92000</v>
       </c>
       <c r="AJ15" s="3">
         <v>92000</v>
       </c>
       <c r="AK15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AL15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2950000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3271000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2999000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2827000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2618000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2868000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2689000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2593000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2401000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2633000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2644000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2479000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2217000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2389000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2268000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2187000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1958000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2062000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1732000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1628000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1798000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2015000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1812000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1716000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1676000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2573000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4300000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4218000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4370000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4134000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3730000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3680000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3844000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3676000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3347000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3184000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3112000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3018000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2950000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2827000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2717000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2341000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2197000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2058000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2105000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1707000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2211000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2399000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2655000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2397000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2213000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1234000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2287000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>32000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>80000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-106000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-67000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>104000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>209000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>243000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>215000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-85000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>84000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-155000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>140000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>173000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>36000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>28000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>25000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>34000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>21000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>26000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>14000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4580000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4450000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4602000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4368000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3949000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3859000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4058000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3878000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3544000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3400000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3377000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3101000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3075000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3120000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3114000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2770000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2460000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2423000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2161000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1936000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2200000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2685000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2734000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2692000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2366000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1375000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2423000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E22" s="3">
         <v>184000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>159000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>153000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>150000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>148000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>151000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>144000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>132000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>127000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>120000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>114000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>110000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>108000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>110000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>106000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>107000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>105000</v>
       </c>
       <c r="U22" s="3">
         <v>105000</v>
       </c>
       <c r="V22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="W22" s="3">
         <v>101000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>69000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>64000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>63000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>51000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>47000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>48000</v>
       </c>
       <c r="AD22" s="3">
         <v>48000</v>
       </c>
       <c r="AE22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>43000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>41000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>39000</v>
       </c>
       <c r="AI22" s="3">
         <v>39000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>30000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4031000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3891000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3866000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3939000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3558000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3321000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3761000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3704000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2853000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3089000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3072000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2798000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2773000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2823000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2816000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2478000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2190000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2168000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1915000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1690000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1987000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2475000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2534000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2519000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2203000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2264000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>751000</v>
+      </c>
+      <c r="E24" s="3">
         <v>549000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>603000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>681000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>547000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>530000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>563000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>859000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>492000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>564000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>573000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>523000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>142000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>444000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>402000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>412000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>362000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>383000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>402000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>270000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>294000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>402000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>426000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>471000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>341000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>391000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>365000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>353000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>311000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>480000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>502000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>451000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>397000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>378000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3280000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3342000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3263000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3258000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3011000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2791000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3198000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2845000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2361000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2525000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2499000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2275000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2631000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2379000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2414000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2066000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1828000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1785000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1513000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1420000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1693000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2073000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2108000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2048000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1862000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>824000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1899000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>933000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3280000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3342000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3263000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3258000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3011000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2791000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3198000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2845000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2361000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2525000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2499000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2275000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2631000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2379000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2414000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2066000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1828000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1785000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1513000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1420000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1693000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2073000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2108000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2048000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1862000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>824000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1899000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>933000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2893,8 +2954,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
@@ -2911,36 +2972,36 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>27000</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>75000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-32000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-80000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>106000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>67000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-104000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-209000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-243000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-215000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>85000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-84000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>155000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-140000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>58000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-173000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>22000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3280000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3342000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3263000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3258000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3011000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2791000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3198000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2845000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2361000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2525000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2499000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2275000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2631000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2379000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2414000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2066000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1828000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1785000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1513000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1420000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1693000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2100000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2108000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2048000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1862000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>899000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1899000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>227000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>933000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3280000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3342000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3263000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3258000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3011000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2791000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3198000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2845000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2361000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2525000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2499000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2275000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2631000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2379000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2414000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2066000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1828000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1785000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1513000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1420000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1693000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2100000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2108000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2048000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1862000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>899000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1899000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>227000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>933000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,329 +3871,339 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7575000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8442000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11063000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6996000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7293000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8588000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6890000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6170000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6566000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7008000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7633000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5921000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6879000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7421000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6406000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6216000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7246000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10113000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10225000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11137000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10207000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6988000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5101000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5691000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5857000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6682000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6871000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E42" s="3">
         <v>330000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>338000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>362000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>364000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>592000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>602000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>344000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>402000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>400000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>412000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>438000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>449000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>473000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>510000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>544000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>489000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>483000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>400000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>390000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>477000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>688000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>751000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>809000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1317000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1696000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1622000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3965000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3773000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4014000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4195000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4231000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4060000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3925000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3763000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3511000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4813000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4264000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4315000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4138000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4459000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3765000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3785000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4398000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4411000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3775000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3971000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3657000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5557000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5274000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4207000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4047000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4728000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3612000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,543 +4309,561 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7438000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6687000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6885000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6227000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6536000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5689000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5566000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5655000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5345000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4385000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4514000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4537000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4487000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4596000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4701000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4534000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4272000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4106000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4069000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3883000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3782000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3669000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3721000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3458000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3175000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3065000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2959000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19804000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19724000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22300000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17780000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18424000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18961000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16983000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16530000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16420000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16606000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16823000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15211000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15953000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16949000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15382000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15079000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16405000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19113000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18469000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19381000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18123000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16902000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14847000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14165000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14396000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16171000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15064000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1598000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1607000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1601000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1709000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1737000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1729000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1650000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1664000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1503000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2805000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2694000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2745000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2986000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2966000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2658000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2479000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2133000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1970000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1613000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1621000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1509000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1526000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1296000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1276000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>722000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>635000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>480000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>441000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>409000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>427000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>388000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>392000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>298000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>307000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2171000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2138000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2176000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2148000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2077000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2061000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1972000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2006000</v>
       </c>
       <c r="L48" s="3">
         <v>2006000</v>
       </c>
       <c r="M48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="N48" s="3">
         <v>1951000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1950000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1957000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1907000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1860000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1839000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1850000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1902000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1887000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1872000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1901000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1828000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1492000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1348000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1305000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>921000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>876000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>860000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>839000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>829000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>901000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>845000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>748000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>733000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14885000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14646000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11956000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11712000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11668000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11746000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11510000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11628000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11602000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11381000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10758000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11195000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11300000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11333000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11130000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11274000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10372000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6713000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5666000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5561000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5517000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5438000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5034000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4756000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3969000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3895000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3973000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1863000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1802000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1560000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1602000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1473000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1426000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1272000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1297000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1423000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5926000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5386000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5130000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4967000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4514000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4380000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4240000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4040000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3886000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3959000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3692000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3598000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3542000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3312000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3186000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3128000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3238000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2947000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48470000</v>
+      </c>
+      <c r="E54" s="3">
         <v>48081000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47237000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42333000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42602000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42448000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>39674000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39004000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38936000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38724000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37612000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36231000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37163000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37669000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35410000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34911000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34800000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33584000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31594000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32127000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30648000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29236000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>25981000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24731000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23520000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>24860000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>23340000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,162 +5491,166 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>993000</v>
+      </c>
+      <c r="E57" s="3">
         <v>929000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>911000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>835000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>790000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>834000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>589000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>643000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>735000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>926000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>615000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>633000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>666000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>738000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>557000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>547000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>476000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>527000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>341000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>369000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>371000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>489000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>505000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>432000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>508000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>537000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>382000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>345000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>370000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>933000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>722000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>654000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>680000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>609000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>883000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>750000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1086000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2086000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1479000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1337000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1336000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>276000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>274000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>957000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>735000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>778000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>792000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>650000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>649000</v>
       </c>
       <c r="S58" s="3">
         <v>649000</v>
@@ -5524,8 +5658,8 @@
       <c r="T58" s="3">
         <v>649000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
+      <c r="U58" s="3">
+        <v>649000</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>5</v>
@@ -5533,8 +5667,8 @@
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5543,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>500000</v>
@@ -5551,8 +5685,8 @@
       <c r="AC58" s="3">
         <v>500000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
+      <c r="AD58" s="3">
+        <v>500000</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>5</v>
@@ -5566,8 +5700,8 @@
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -5575,436 +5709,451 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8309000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7469000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6882000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5979000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6609000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5920000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5373000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5989000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5918000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12971000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11904000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10717000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10484000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11632000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10354000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10101000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10350000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10671000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9617000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9554000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9341000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11415000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10209000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9065000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9238000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10556000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8827000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17828000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19220000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17294000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15594000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16905000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16264000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14519000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14636000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13651000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14171000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13476000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12085000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11928000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13162000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11561000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11297000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11475000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11847000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9958000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9923000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9712000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11904000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10714000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9497000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10246000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11593000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9709000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18802000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18103000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17608000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14519000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13543000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14977000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14229000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14284000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15292000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13749000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13577000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13746000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13868000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13109000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13211000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13250000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13221000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12023000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12574000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12498000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12466000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8527000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7735000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7806000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5799000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>5858000</v>
       </c>
       <c r="AD61" s="3">
         <v>5858000</v>
       </c>
       <c r="AE61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4365000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3477000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4102000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4068000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4155000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3523000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3860000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3820000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3931000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4427000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4116000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4138000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4237000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3986000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3836000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3795000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3651000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3197000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3181000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3158000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2972000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2814000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2483000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2319000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2212000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1944000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1906000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>999000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>982000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>621000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>605000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41774000</v>
+      </c>
+      <c r="E66" s="3">
         <v>41566000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39739000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34851000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35294000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35451000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33293000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33425000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33529000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32426000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31251000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30060000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30129000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30357000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28707000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28469000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28473000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>27193000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25798000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25657000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25250000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23343000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21032000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19723000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18352000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19465000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17565000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>75495000</v>
+      </c>
+      <c r="E72" s="3">
         <v>72907000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>70258000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>67604000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>64959000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>62564000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>60390000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>57730000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>55424000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53607000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>51625000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>49599000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>47800000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>45648000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43750000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41771000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40140000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38747000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37403000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36288000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>35273000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33984000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>32289000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>30517000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>28806000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>27283000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>26726000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6671000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6485000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7440000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7421000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7243000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6929000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6311000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5504000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5330000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6298000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6361000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6171000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7034000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7312000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6703000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6442000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6327000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6391000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5796000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6470000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5398000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5893000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4949000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5008000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5168000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5395000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5775000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3280000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3342000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3263000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3258000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3011000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2791000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3198000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2845000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2361000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2525000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2499000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2275000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2631000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2379000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2414000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2066000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1828000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1785000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1513000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1420000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1693000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2100000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2108000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2048000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1862000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>899000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1899000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>227000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>933000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>216000</v>
+      </c>
+      <c r="E83" s="3">
         <v>346000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>211000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>192000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>191000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>321000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>185000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>189000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>192000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>184000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>185000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>189000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>192000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>189000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>188000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>186000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>163000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>150000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>141000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>145000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>144000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>146000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>137000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>122000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>117000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>113000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>111000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>115000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>120000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>116000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>118000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>92000</v>
       </c>
       <c r="AJ83" s="3">
         <v>92000</v>
       </c>
       <c r="AK83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AL83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2380000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4834000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5136000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3138000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1672000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4130000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3233000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2698000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1919000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3100000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3856000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2457000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1782000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3189000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2543000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2268000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1463000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2253000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1654000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1458000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1859000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2980000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2355000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1536000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1332000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2367000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>745000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>992000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-159000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-95000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-107000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-115000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-157000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-104000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-80000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-110000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-339000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-277000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-187000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-294000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-228000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-249000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-81000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-65000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-59000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-79000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-70000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-131000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-116000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-132000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-340000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2678000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-256000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-294000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-174000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-214000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-522000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-218000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-397000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-350000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-308000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-525000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-287000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-438000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-132000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-199000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-119000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-507000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-460000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-626000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>213000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>367000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,49 +9286,50 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>694000</v>
+      </c>
+      <c r="E96" s="3">
         <v>606000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>611000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>615000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>616000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>534000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>538000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>541000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>545000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-473000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-474000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-477000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-434000</v>
       </c>
       <c r="Q96" s="3">
         <v>-434000</v>
@@ -9104,64 +9338,67 @@
         <v>-434000</v>
       </c>
       <c r="S96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-439000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-399000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-402000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-401000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-403000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-333000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-335000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-337000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-259000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2987000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4041000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-857000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3257000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-606000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-409000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2100000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-582000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-937000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>675000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E101" s="3">
         <v>157000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-86000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>20000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>284000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-185000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-174000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-28000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>284000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-185000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-174000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-28000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-56000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>77000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-101000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>191000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>115000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>39000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-88000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>59000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-77000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>28000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-54000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-71000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>95000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>71000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>88000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-826000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2159000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4165000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-385000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1278000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1723000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>221000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-279000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-396000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-580000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1624000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-687000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1061000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>218000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-992000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-898000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>969000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3364000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1997000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-473000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-140000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-752000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-141000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>710000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>832000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>401000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>440000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,272 +656,279 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8133000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7250000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7489000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7369000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6961000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6348000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6548000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6533000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6269000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5748000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5817000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5756000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5497000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5167000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5216000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4985000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4528000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4155000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4120000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3837000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3335000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4009000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4414000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4467000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4113000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3889000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3807000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3898000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1030,41 +1037,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8133000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7250000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7489000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7369000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6961000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6348000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6548000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6533000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6269000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5748000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,77 +1417,80 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E14" s="3">
         <v>180000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>240000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>428000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>111000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>120000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>274000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-103000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>423000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>208000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>166000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>34000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>27000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>67000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>45000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>22000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
@@ -1481,20 +1501,20 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>757000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>29000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>225000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>117000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1502,126 +1522,132 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>15000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>10000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>281000</v>
+      </c>
+      <c r="E15" s="3">
         <v>275000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>231000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>225000</v>
       </c>
       <c r="G15" s="3">
         <v>225000</v>
       </c>
       <c r="H15" s="3">
+        <v>225000</v>
+      </c>
+      <c r="I15" s="3">
         <v>216000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>205000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>211000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>192000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>191000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>184000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>185000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>189000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>192000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>189000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>188000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>186000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>163000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>150000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>141000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>145000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>144000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>146000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>137000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>122000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>117000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>113000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>111000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>115000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>120000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>115000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>118000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>92000</v>
       </c>
       <c r="AK15" s="3">
         <v>92000</v>
       </c>
       <c r="AL15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AM15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3260000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2950000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3271000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2999000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2827000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2618000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2868000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2689000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2593000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2401000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2633000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2644000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2479000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2217000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2389000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2268000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2187000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1958000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2062000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1732000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1628000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1798000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2015000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1812000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1716000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1676000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2573000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4873000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4300000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4218000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4370000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4134000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3730000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3680000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3844000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3676000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3347000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3184000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3112000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3018000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2950000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2827000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2717000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2341000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2197000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2058000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2105000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1707000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2211000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2399000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2655000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2397000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2213000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1234000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2287000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>32000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>80000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-106000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>104000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>209000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>243000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>215000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-85000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>84000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-155000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>140000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>173000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>36000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>28000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>25000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>21000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>26000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>11000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5170000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4580000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4450000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4602000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4368000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3949000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3859000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4058000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3878000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3544000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3400000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3377000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3101000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3075000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3120000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3114000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2770000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2460000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2423000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2161000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1936000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2200000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2685000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2734000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2692000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2366000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1375000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2423000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E22" s="3">
         <v>182000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>184000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>159000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>153000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>150000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>148000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>151000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>144000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>132000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>127000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>120000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>114000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>110000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>108000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>110000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>106000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>107000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>105000</v>
       </c>
       <c r="V22" s="3">
         <v>105000</v>
       </c>
       <c r="W22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="X22" s="3">
         <v>101000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>69000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>64000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>63000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>51000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>46000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>47000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>48000</v>
       </c>
       <c r="AE22" s="3">
         <v>48000</v>
       </c>
       <c r="AF22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>43000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>41000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>39000</v>
       </c>
       <c r="AJ22" s="3">
         <v>39000</v>
       </c>
       <c r="AK22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AL22" s="3">
         <v>30000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4672000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4031000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3891000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3866000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3939000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3558000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3321000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3761000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3704000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2853000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3089000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3072000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2798000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2773000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2823000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2816000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2478000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2190000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2168000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1915000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1690000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1987000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2475000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2534000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2519000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2203000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2264000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>971000</v>
+      </c>
+      <c r="E24" s="3">
         <v>751000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>549000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>603000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>681000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>547000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>530000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>563000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>859000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>492000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>564000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>573000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>523000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>142000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>444000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>402000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>412000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>362000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>383000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>402000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>270000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>294000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>402000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>426000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>471000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>341000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>391000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>365000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>353000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>311000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>480000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>502000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>451000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>397000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>378000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3701000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3280000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3342000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3263000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3258000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3011000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2791000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3198000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2845000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2361000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2525000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2499000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2275000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2631000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2379000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2414000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2066000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1828000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1785000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1513000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1420000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1693000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2073000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2108000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2048000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>824000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1899000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>933000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3701000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3280000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3342000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3263000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3258000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3011000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2791000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3198000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2845000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2361000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2525000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2499000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2275000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2631000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2379000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2414000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2066000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1828000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1785000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1513000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1420000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1693000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2073000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2108000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2048000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>824000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1899000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>933000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2957,8 +3018,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -2975,36 +3036,36 @@
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>27000</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>75000</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-32000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-80000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>106000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>67000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-104000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-209000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-243000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-215000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>85000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-84000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>155000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-140000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>58000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-173000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>22000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3701000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3280000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3342000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3263000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3258000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3011000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2791000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3198000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2845000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2361000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2525000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2499000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2275000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2631000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2379000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2414000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2066000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1828000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1785000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1513000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1420000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1693000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2100000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2108000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2048000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>899000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1899000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>227000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>933000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3701000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3280000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3342000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3263000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3258000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3011000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2791000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3198000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2845000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2361000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2525000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2499000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2275000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2631000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2379000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2414000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2066000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1828000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1785000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1513000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1420000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1693000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2100000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2108000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2048000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>899000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1899000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>227000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>933000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,338 +3958,348 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9031000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7575000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8442000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11063000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6996000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7293000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8588000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6890000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6170000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6566000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7008000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7633000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5921000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6879000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7421000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6406000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6216000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7246000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10113000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10225000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11137000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10207000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6988000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5101000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5691000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5857000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6682000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6871000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>336000</v>
+      </c>
+      <c r="E42" s="3">
         <v>319000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>330000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>338000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>362000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>364000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>592000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>602000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>344000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>402000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>400000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>412000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>438000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>449000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>473000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>510000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>544000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>489000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>483000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>400000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>390000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>477000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>688000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>751000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>809000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1317000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1696000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1622000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4184000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3965000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3773000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4014000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4195000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4231000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4060000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3925000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3763000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3511000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4813000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4264000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4315000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4138000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4459000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3765000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3785000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4398000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4411000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3775000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3971000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3657000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5557000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5274000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4207000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4047000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4728000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3612000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,558 +4408,576 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8047000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7438000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6687000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6885000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6227000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6536000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5689000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5566000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5655000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5345000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4385000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4514000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4537000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4487000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4596000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4701000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4534000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4272000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4106000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4069000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3883000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3782000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3669000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3721000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3458000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3175000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3065000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2959000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22140000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19804000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19724000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22300000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17780000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18424000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18961000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16983000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16530000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16420000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16606000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16823000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15211000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15953000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16949000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15382000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15079000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16405000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19113000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18469000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19381000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18123000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16902000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14847000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14165000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14396000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16171000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15064000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1598000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1607000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1601000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1709000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1737000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1729000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1650000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1664000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1503000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2805000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2694000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2745000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2986000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2966000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2658000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2479000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2133000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1970000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1613000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1621000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1509000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1526000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1296000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1276000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>722000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>635000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>480000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>441000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>409000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>427000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>388000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>392000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>298000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>307000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2225000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2171000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2138000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2176000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2148000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2077000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2061000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1972000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>2006000</v>
       </c>
       <c r="M48" s="3">
         <v>2006000</v>
       </c>
       <c r="N48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="O48" s="3">
         <v>1951000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1950000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1957000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1907000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1860000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1839000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1850000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1902000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1887000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1872000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1901000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1828000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1348000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1305000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>921000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>876000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>860000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>839000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>829000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>901000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>845000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>748000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>733000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15227000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14885000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14646000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11956000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11712000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11668000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11746000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11510000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11628000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11602000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11381000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10758000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11195000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11300000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11333000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11130000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11274000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10372000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6713000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5666000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5561000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5517000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5438000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5034000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4756000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3969000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3895000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3973000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1836000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1863000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1802000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1560000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1602000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1473000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1426000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1272000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1297000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1423000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5926000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5386000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5130000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4967000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4514000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4380000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4240000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4040000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3886000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3959000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3692000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3598000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3542000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3312000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3186000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3128000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3238000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2947000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51431000</v>
+      </c>
+      <c r="E54" s="3">
         <v>48470000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48081000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47237000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42333000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42602000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42448000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39674000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39004000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38936000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38724000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37612000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36231000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37163000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37669000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35410000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34911000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34800000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33584000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31594000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32127000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>30648000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29236000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25981000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24731000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23520000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>24860000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23340000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,118 +5622,122 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>818000</v>
+      </c>
+      <c r="E57" s="3">
         <v>993000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>929000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>911000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>835000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>790000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>834000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>589000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>643000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>735000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>926000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>615000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>633000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>666000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>738000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>557000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>547000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>476000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>527000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>341000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>369000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>371000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>489000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>505000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>432000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>508000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>537000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>382000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>345000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>370000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>933000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>722000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>654000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>680000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>609000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5611,49 +5745,49 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>883000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>750000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1086000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2086000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1479000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1337000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1336000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>276000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>274000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>957000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>735000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>778000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>792000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>650000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>649000</v>
       </c>
       <c r="T58" s="3">
         <v>649000</v>
@@ -5661,8 +5795,8 @@
       <c r="U58" s="3">
         <v>649000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
+      <c r="V58" s="3">
+        <v>649000</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
@@ -5670,8 +5804,8 @@
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5680,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>500000</v>
@@ -5688,8 +5822,8 @@
       <c r="AD58" s="3">
         <v>500000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
+      <c r="AE58" s="3">
+        <v>500000</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>5</v>
@@ -5703,8 +5837,8 @@
       <c r="AI58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
@@ -5712,448 +5846,463 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8587000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8309000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7469000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6882000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5979000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6609000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5920000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5373000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5989000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5918000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12971000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11904000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10717000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10484000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11632000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10354000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10101000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10350000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10671000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9617000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9554000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9341000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11415000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10209000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9065000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9238000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10556000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8827000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19029000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17828000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19220000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17294000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15594000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16905000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16264000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14519000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14636000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13651000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14171000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13476000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12085000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11928000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13162000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11561000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11297000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11475000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11847000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9958000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9923000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9712000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11904000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10714000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9497000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10246000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11593000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9709000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18970000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18802000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18103000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17608000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14519000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13543000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14977000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14229000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14284000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15292000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13749000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13577000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13746000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13868000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13109000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13211000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13250000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13221000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12023000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12574000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12498000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12466000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8527000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7735000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7806000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5799000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>5858000</v>
       </c>
       <c r="AE61" s="3">
         <v>5858000</v>
       </c>
       <c r="AF61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4799000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4365000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3477000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4102000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4068000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4155000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3523000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3860000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3820000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3931000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4427000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4116000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4138000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4237000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3986000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3836000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3795000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3651000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3197000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3181000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3158000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2972000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2814000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2483000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2319000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2212000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1944000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1906000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>999000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>982000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>621000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>605000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43557000</v>
+      </c>
+      <c r="E66" s="3">
         <v>41774000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41566000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39739000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34851000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35294000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35451000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33293000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33425000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33529000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32426000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31251000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30060000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30129000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30357000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28707000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28469000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28473000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27193000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25798000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25657000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25250000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23343000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21032000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19723000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18352000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19465000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17565000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>78509000</v>
+      </c>
+      <c r="E72" s="3">
         <v>75495000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>72907000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>70258000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>67604000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>64959000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>62564000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>60390000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57730000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>55424000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53607000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51625000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>49599000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>47800000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>45648000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>43750000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>41771000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>40140000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38747000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>37403000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36288000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35273000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33984000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>32289000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>30517000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>28806000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>27283000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>26726000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7853000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6671000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6485000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7440000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7421000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7243000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6929000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6311000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5504000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5330000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6298000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6361000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6171000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7034000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7312000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6703000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6442000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6327000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6391000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5796000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6470000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5398000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5893000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4949000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5008000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5168000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5395000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5775000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3701000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3280000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3342000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3263000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3258000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3011000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2791000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3198000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2845000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2361000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2525000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2499000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2275000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2631000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2379000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2414000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2066000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1828000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1785000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1513000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1420000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1693000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2100000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2108000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2048000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>899000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1899000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>227000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>933000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E83" s="3">
         <v>216000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>346000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>211000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>192000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>191000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>321000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>185000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>189000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>192000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>184000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>185000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>189000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>192000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>189000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>188000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>186000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>163000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>150000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>141000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>145000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>144000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>146000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>137000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>122000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>117000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>113000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>111000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>115000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>120000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>116000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>118000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>92000</v>
       </c>
       <c r="AK83" s="3">
         <v>92000</v>
       </c>
       <c r="AL83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AM83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4603000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2380000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4834000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5136000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3138000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1672000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4130000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3233000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2698000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1919000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3100000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3856000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2457000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1782000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3189000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2543000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2268000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1463000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2253000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1654000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1458000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1859000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2980000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1536000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1332000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2367000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>745000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>992000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-159000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-95000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-107000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-115000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-157000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-77000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-104000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-80000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-110000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-339000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-277000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-187000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-294000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-228000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-249000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-81000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-65000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-59000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-79000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-70000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-131000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-116000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-132000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-227000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-340000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2678000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-256000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-294000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-174000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-214000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-522000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-218000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-397000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-350000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-308000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-525000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-287000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-438000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-132000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-199000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-119000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-507000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-460000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-626000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>213000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>367000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,52 +9520,53 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>691000</v>
+      </c>
+      <c r="E96" s="3">
         <v>694000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>606000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>611000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>615000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>616000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>534000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>538000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>541000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>545000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-473000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-474000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-477000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-434000</v>
       </c>
       <c r="R96" s="3">
         <v>-434000</v>
@@ -9341,64 +9575,67 @@
         <v>-434000</v>
       </c>
       <c r="T96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-439000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-399000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-402000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-401000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-403000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-333000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-335000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-337000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-259000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3006000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2987000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4041000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-857000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3257000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-606000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-409000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2100000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-582000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-937000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>675000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-95000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>157000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-86000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>20000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>37000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>284000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-185000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-174000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-28000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>284000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-185000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-174000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-73000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-56000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>77000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-101000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>191000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>115000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>39000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-88000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>59000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>28000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-54000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-71000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>95000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>71000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>35000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1590000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-826000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2159000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4165000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-385000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1278000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1723000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>221000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-279000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-396000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-580000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1624000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-687000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1061000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>218000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-992000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-898000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>969000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3364000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1997000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-473000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-140000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-752000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-141000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>710000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>832000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>401000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>440000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,286 +656,292 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8806000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8602000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8133000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7250000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7489000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7369000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6961000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6348000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6548000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6533000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6269000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5748000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5817000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5756000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5497000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5167000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5216000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4985000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4528000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4155000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4120000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3837000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3335000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4009000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4414000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4467000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4113000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3889000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3807000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3898000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1050,47 +1056,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8806000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8602000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8133000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7250000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7489000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7369000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6961000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6348000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6548000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6533000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6269000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5748000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1166,8 +1175,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,83 +1456,86 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E14" s="3">
         <v>42000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>92000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>180000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>240000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>428000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>111000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>120000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>274000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-103000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>423000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>208000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>166000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>34000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>27000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>67000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>45000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>22000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1527,20 +1546,20 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>757000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>29000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>225000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>117000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
@@ -1548,132 +1567,138 @@
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>15000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>10000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>297000</v>
+      </c>
+      <c r="E15" s="3">
         <v>290000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>281000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>275000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>231000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>225000</v>
       </c>
       <c r="I15" s="3">
         <v>225000</v>
       </c>
       <c r="J15" s="3">
+        <v>225000</v>
+      </c>
+      <c r="K15" s="3">
         <v>216000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>205000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>211000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>192000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>191000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>184000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>185000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>189000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>192000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>189000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>188000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>186000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>163000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>150000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>141000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>145000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>144000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>146000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>137000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>122000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>117000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>113000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>111000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>115000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>120000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>115000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>118000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>92000</v>
       </c>
       <c r="AM15" s="3">
         <v>92000</v>
       </c>
       <c r="AN15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3722000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3458000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3260000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2950000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3271000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2999000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2827000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2618000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2868000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2689000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2593000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2401000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2633000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2644000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2479000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2217000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2389000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2268000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2187000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1958000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2062000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1732000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1628000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1798000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2015000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1812000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1716000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1676000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2573000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5084000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5144000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4873000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4300000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4218000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4370000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4134000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3730000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3680000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3844000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3676000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3347000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3184000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3112000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3018000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2950000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2827000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2717000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2341000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2197000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2058000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2105000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1707000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2211000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2399000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2655000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2397000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2213000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1234000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2287000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,588 +2017,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-143000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-16000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>26000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>32000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>80000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-106000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-67000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>104000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>209000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>243000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>215000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-85000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>84000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-155000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>140000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>173000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>36000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>28000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>25000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>34000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>21000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>26000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>14000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>11000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5524000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5436000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5170000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4580000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4450000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4602000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4368000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3949000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3859000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4058000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3878000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3544000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3400000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3377000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3101000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3075000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3120000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3114000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2770000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2460000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2423000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2161000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1936000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2200000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2685000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2734000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2692000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2366000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1375000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2423000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E22" s="3">
         <v>186000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>195000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>182000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>184000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>159000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>153000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>150000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>148000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>151000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>144000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>132000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>127000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>120000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>114000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>110000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>108000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>110000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>106000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>107000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>105000</v>
       </c>
       <c r="X22" s="3">
         <v>105000</v>
       </c>
       <c r="Y22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>101000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>69000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>64000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>63000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>51000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>47000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>48000</v>
       </c>
       <c r="AG22" s="3">
         <v>48000</v>
       </c>
       <c r="AH22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>43000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>41000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>39000</v>
       </c>
       <c r="AL22" s="3">
         <v>39000</v>
       </c>
       <c r="AM22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AN22" s="3">
         <v>30000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4876000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4999000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4672000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4031000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3891000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3866000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3939000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3558000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3321000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3761000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3704000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2853000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3089000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3072000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2798000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2773000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2823000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2816000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2478000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2190000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2168000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1915000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1690000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1987000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2475000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2534000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2519000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2203000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2264000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1072000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>971000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>751000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>549000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>603000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>681000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>547000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>530000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>563000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>859000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>492000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>564000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>573000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>523000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>142000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>444000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>402000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>412000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>362000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>383000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>402000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>270000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>294000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>402000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>426000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>471000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>341000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>391000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>365000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>353000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>311000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>480000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>502000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>451000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>397000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>378000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4060000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3927000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3701000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3280000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3342000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3263000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3258000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3011000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2791000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3198000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2845000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2361000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2525000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2499000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2275000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2631000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2379000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2414000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2066000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1828000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1785000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1513000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1420000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1693000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2073000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2108000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2048000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1862000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>824000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1899000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>933000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4060000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3927000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3701000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3280000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3342000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3263000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3258000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3011000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2791000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3198000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2845000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2361000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2525000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2499000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2275000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2631000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2379000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2414000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2066000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1828000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1785000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1513000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1420000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1693000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2073000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2108000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2048000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1862000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>824000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1899000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>933000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3085,8 +3145,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -3103,36 +3163,36 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>27000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>75000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3443,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>16000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-26000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-32000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>106000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>67000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-104000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-209000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-243000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-215000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>85000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>155000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-140000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>58000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-173000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>22000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4060000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3927000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3701000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3280000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3342000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3263000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3258000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3011000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2791000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3198000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2845000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2361000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2525000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2499000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2275000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2631000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2379000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2414000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2066000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1828000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1785000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1513000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1420000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1693000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2100000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2108000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2048000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1862000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>899000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1899000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>933000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4060000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3927000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3701000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3280000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3342000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3263000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3258000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3011000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2791000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3198000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2845000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2361000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2525000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2499000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2275000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2631000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2379000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2414000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2066000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1828000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1785000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1513000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1420000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1693000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2100000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2108000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2048000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1862000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>899000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1899000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>933000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,356 +4131,366 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10566000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10313000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9031000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7575000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8442000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11063000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6996000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7293000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8588000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6890000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6170000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6566000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7008000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7633000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5921000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6879000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7421000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6406000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6216000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7246000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10113000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10225000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11137000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10207000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6988000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5101000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5691000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5857000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6682000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6871000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E42" s="3">
         <v>335000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>336000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>319000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>330000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>338000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>362000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>364000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>592000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>602000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>344000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>402000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>400000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>412000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>438000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>449000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>473000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>510000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>544000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>489000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>483000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>400000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>390000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>477000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>688000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>751000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>809000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1317000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1696000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1622000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4609000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4247000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4184000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3965000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3773000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4014000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4195000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4231000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4060000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3925000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3763000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3511000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4813000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4264000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4315000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4138000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4459000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3765000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3785000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4398000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4411000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3775000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3971000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3657000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5557000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5274000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4207000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4047000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4728000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3612000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,588 +4605,606 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7490000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7850000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8047000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7438000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6687000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6885000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6227000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6536000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5689000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5566000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5655000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5345000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4385000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4514000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4537000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4487000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4596000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4701000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4534000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4272000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4106000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4069000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3883000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3782000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3669000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3721000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3458000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3175000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3065000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2959000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23558000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23223000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22140000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19804000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19724000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22300000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17780000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18424000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18961000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16983000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16530000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16420000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16606000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16823000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15211000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15953000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16949000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15382000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15079000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16405000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19113000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18469000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19381000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18123000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16902000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14847000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14165000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14396000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16171000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15064000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1705000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1685000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1638000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1598000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1607000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1601000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1709000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1737000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1729000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1650000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1664000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1503000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2805000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2694000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2745000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2986000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2966000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2658000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2479000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2133000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1970000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1613000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1621000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1509000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1526000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1296000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>722000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>635000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>480000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>441000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>409000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>427000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>388000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>392000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>298000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>307000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2303000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2299000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2225000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2171000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2138000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2176000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2148000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2077000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2061000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1972000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>2006000</v>
       </c>
       <c r="O48" s="3">
         <v>2006000</v>
       </c>
       <c r="P48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1951000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1950000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1957000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1907000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1860000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1839000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1850000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1902000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1887000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1872000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1901000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1828000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1348000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1305000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>921000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>876000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>860000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>839000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>829000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>901000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>845000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>748000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>733000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15114000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15165000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15227000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14885000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14646000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11956000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11712000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11668000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11746000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11510000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11628000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11602000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11381000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10758000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11195000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11300000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11333000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11130000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11274000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10372000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6713000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5666000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5561000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5517000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5438000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5034000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4756000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3969000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3895000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3973000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1674000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1836000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1863000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1802000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1560000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1602000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1473000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1426000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1272000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1297000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1423000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5926000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5386000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5130000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4967000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4514000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4380000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4240000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4040000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3886000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3959000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3692000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3598000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3542000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3312000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3186000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3128000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3238000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2947000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54157000</v>
+      </c>
+      <c r="E54" s="3">
         <v>53289000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51431000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48470000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48081000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47237000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42333000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42602000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42448000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39674000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39004000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>38936000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38724000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37612000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36231000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37163000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37669000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35410000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34911000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34800000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33584000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>31594000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32127000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30648000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29236000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25981000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>24731000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23520000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>24860000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23340000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,129 +5883,133 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>999000</v>
+      </c>
+      <c r="E57" s="3">
         <v>935000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>818000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>993000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>929000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>911000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>835000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>790000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>834000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>589000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>643000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>735000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>926000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>615000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>633000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>666000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>738000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>557000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>547000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>476000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>527000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>341000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>369000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>371000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>489000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>505000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>432000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>508000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>537000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>382000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>345000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>370000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>933000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>722000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>654000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>680000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>609000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>906000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -5885,49 +6018,49 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>883000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>750000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1086000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2086000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1479000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1337000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1336000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>276000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>274000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>957000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>735000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>778000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>792000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>650000</v>
-      </c>
-      <c r="U58" s="3">
-        <v>649000</v>
       </c>
       <c r="V58" s="3">
         <v>649000</v>
@@ -5935,8 +6068,8 @@
       <c r="W58" s="3">
         <v>649000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
+      <c r="X58" s="3">
+        <v>649000</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>5</v>
@@ -5944,8 +6077,8 @@
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5954,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>500000</v>
@@ -5962,8 +6095,8 @@
       <c r="AF58" s="3">
         <v>500000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
+      <c r="AG58" s="3">
+        <v>500000</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>5</v>
@@ -5977,8 +6110,8 @@
       <c r="AK58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AL58" s="3">
-        <v>0</v>
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM58" s="3">
         <v>0</v>
@@ -5986,472 +6119,487 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8499000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8492000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8587000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8309000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7469000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6882000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5979000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6609000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5920000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5373000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5989000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5918000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12971000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11904000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10717000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10484000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11632000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10354000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10101000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10350000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10671000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9617000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9554000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9341000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11415000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10209000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9065000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9238000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10556000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8827000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22762000</v>
+      </c>
+      <c r="E60" s="3">
         <v>20693000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19029000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17828000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19220000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17294000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15594000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16905000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16264000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14519000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14636000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13651000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14171000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13476000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12085000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11928000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13162000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11561000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11297000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11475000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11847000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9958000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9923000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9712000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11904000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10714000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9497000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10246000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11593000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9709000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18927000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18983000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18970000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18802000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18103000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17608000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14519000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13543000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14977000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14229000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14284000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15292000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13749000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13577000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13746000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13868000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13109000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13211000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13250000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13221000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12023000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12574000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12498000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12466000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8527000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7735000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7806000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5799000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>5858000</v>
       </c>
       <c r="AG61" s="3">
         <v>5858000</v>
       </c>
       <c r="AH61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3991000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4990000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4799000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4365000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3477000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4102000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4068000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4155000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3523000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3860000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3820000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3931000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4427000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4116000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4138000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4237000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3986000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3836000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3795000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3651000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3197000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3181000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3158000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2972000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2814000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2483000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2319000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2212000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1944000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1906000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>999000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>982000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>621000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>605000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46411000</v>
+      </c>
+      <c r="E66" s="3">
         <v>45370000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43557000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41774000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41566000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39739000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34851000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35294000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35451000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33293000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33425000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33529000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32426000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31251000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30060000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30129000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30357000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28707000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28469000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28473000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>27193000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25798000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25657000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>25250000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23343000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21032000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19723000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18352000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19465000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17565000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>85035000</v>
+      </c>
+      <c r="E72" s="3">
         <v>81752000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>78509000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>75495000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>72907000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>70258000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>67604000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>64959000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>62564000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>60390000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>57730000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>55424000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53607000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>51625000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>49599000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47800000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>45648000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>43750000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41771000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>40140000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38747000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>37403000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>36288000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35273000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33984000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>32289000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>30517000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>28806000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>27283000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26726000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7737000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7904000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7853000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6671000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6485000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7440000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7421000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7243000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6929000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6311000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5504000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5330000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6298000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6361000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6171000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7034000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7312000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6703000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6442000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6327000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6391000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5796000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6470000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5398000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5893000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4949000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5008000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5168000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5395000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5775000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4060000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3927000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3701000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3280000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3342000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3263000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3258000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3011000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2791000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3198000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2845000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2361000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2525000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2499000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2275000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2631000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2379000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2414000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2066000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1828000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1785000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1513000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1420000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1693000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2100000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2108000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2048000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1862000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>899000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1899000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>933000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>225000</v>
+        <v>376000</v>
       </c>
       <c r="E83" s="3">
         <v>225000</v>
       </c>
       <c r="F83" s="3">
+        <v>225000</v>
+      </c>
+      <c r="G83" s="3">
         <v>216000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>346000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>211000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>192000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>191000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>321000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>185000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>189000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>192000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>184000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>185000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>189000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>192000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>189000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>188000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>186000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>163000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>150000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>141000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>145000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>144000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>146000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>137000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>122000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>117000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>113000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>111000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>115000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>120000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>116000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>118000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>92000</v>
       </c>
       <c r="AM83" s="3">
         <v>92000</v>
       </c>
       <c r="AN83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AO83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5002000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5663000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4603000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2380000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4834000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5136000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3138000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1672000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4130000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3233000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2698000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1919000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3100000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3856000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2457000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1782000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3189000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2543000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2268000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1463000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2253000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1654000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1458000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1859000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2980000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1536000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1332000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2367000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>745000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>992000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-178000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-40000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-159000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-95000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-107000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-115000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-157000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-77000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-104000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-80000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-110000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-339000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-277000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-187000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-294000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-228000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-249000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-81000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-65000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-59000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-79000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-131000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-116000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-132000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-421000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-374000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-227000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-340000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2678000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-256000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-294000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-174000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-214000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-522000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-218000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-397000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-350000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-308000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-525000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-287000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-438000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-132000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-199000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-507000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-460000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-626000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>213000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>367000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,58 +9987,59 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>684000</v>
+      </c>
+      <c r="E96" s="3">
         <v>687000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>691000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>694000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>606000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>611000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>615000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>616000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>534000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>538000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>541000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>545000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-473000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-474000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-477000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-434000</v>
       </c>
       <c r="T96" s="3">
         <v>-434000</v>
@@ -9815,64 +10048,67 @@
         <v>-434000</v>
       </c>
       <c r="V96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-439000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-399000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-402000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-401000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-403000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-333000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-335000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-337000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-259000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4186000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4000000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3006000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2987000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4041000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-857000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3257000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-606000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-409000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2100000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-582000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-937000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>675000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-274000</v>
+      </c>
+      <c r="E101" s="3">
         <v>142000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>28000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-95000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>157000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-86000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>20000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>37000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>284000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-185000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-174000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>284000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-185000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-174000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-28000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-73000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-56000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>77000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-101000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>191000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>115000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>39000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-88000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>59000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-77000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>28000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-54000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-71000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>95000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>71000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>88000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>35000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1273000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1590000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-826000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2159000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4165000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-385000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1278000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1723000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>221000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-279000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-396000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-580000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1624000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-687000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1061000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>218000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-992000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-898000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>969000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3364000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1997000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-473000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-140000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-752000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-141000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>710000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>832000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>401000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>440000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>29000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>MA</t>
   </si>
@@ -656,292 +656,299 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8398000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8806000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8602000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8133000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7250000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7489000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7369000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6961000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6348000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6548000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6533000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6269000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5748000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5817000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5756000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5497000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5167000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5216000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4985000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4528000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4155000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4120000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3837000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3335000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4009000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4414000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4467000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4113000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3889000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3807000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3898000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3665000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3580000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3312000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3398000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3053000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2734000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2756000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1059,50 +1066,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8398000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8806000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8602000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8133000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7250000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7489000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7369000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6961000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6348000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6548000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6533000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6269000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5748000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1178,8 +1188,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,86 +1476,89 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E14" s="3">
         <v>278000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>42000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>92000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>180000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>240000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>428000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>111000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>120000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>274000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-103000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>423000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>208000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>166000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>34000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>27000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>67000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>45000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>22000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1549,20 +1569,20 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>757000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>29000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>225000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>117000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
@@ -1570,135 +1590,141 @@
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>15000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>10000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E15" s="3">
         <v>297000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>290000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>281000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>275000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>231000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>225000</v>
       </c>
       <c r="J15" s="3">
         <v>225000</v>
       </c>
       <c r="K15" s="3">
+        <v>225000</v>
+      </c>
+      <c r="L15" s="3">
         <v>216000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>205000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>211000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>192000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>191000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>184000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>185000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>189000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>192000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>189000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>188000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>186000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>163000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>150000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>141000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>145000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>144000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>146000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>137000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>122000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>117000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>113000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>111000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>115000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>120000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>115000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>118000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>111000</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>92000</v>
       </c>
       <c r="AN15" s="3">
         <v>92000</v>
       </c>
       <c r="AO15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AP15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3289000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3722000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3458000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3260000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2950000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3271000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2999000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2827000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2618000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2868000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2689000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2593000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2401000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2633000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2644000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2479000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2217000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2389000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2268000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2187000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1958000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2062000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1732000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1628000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1798000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2015000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1812000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1716000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1676000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2573000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1611000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1729000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1755000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1790000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1457000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1400000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1228000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1393000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1210000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5109000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5084000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5144000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4873000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4300000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4218000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4370000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4134000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3730000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3680000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3844000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3676000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3347000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3184000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3112000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3018000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2950000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2827000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2717000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2341000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2197000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2058000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2105000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1707000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2211000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2399000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2655000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2397000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2213000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1234000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2287000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1936000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1825000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1941000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1653000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1506000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1363000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1670000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,603 +2051,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-143000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>26000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>32000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>80000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-106000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-67000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>104000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>209000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>243000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>215000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-85000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>84000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-155000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>140000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>173000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>36000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>28000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>25000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>34000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>26000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>14000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>11000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5483000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5524000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5436000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5170000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4580000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4450000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4602000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4368000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3949000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3859000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4058000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3878000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3544000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3400000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3377000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3101000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3075000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3120000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3114000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2770000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2460000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2423000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2161000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1936000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2200000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2685000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2734000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2692000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2366000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1375000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2423000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1966000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1641000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2085000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1778000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1609000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1433000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E22" s="3">
         <v>159000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>186000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>195000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>182000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>184000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>159000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>153000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>150000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>148000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>151000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>144000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>132000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>127000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>120000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>114000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>110000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>108000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>110000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>106000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>107000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>105000</v>
       </c>
       <c r="Y22" s="3">
         <v>105000</v>
       </c>
       <c r="Z22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>101000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>69000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>64000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>63000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>51000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>47000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>48000</v>
       </c>
       <c r="AH22" s="3">
         <v>48000</v>
       </c>
       <c r="AI22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>41000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>35000</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>39000</v>
       </c>
       <c r="AM22" s="3">
         <v>39000</v>
       </c>
       <c r="AN22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AO22" s="3">
         <v>30000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4812000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4876000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4999000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4672000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4031000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3891000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3866000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3939000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3558000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3321000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3761000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3704000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2853000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3089000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3072000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2798000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2773000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2823000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2816000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2478000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2190000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2168000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1915000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1690000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1987000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2475000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2534000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2519000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2203000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2264000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1922000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1803000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1484000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1932000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1628000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1478000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1633000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>930000</v>
+      </c>
+      <c r="E24" s="3">
         <v>816000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1072000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>971000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>751000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>549000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>603000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>681000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>547000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>530000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>563000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>859000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>492000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>564000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>573000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>523000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>142000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>444000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>402000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>412000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>362000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>383000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>402000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>270000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>294000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>402000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>426000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>471000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>341000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>391000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>365000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>353000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>311000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>480000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>502000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>451000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>397000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>378000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3882000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4060000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3927000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3701000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3280000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3342000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3263000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3258000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3011000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2791000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3198000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2845000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2361000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2525000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2499000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2275000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2631000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2379000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2414000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2066000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1828000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1513000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1420000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1693000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2073000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2108000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2048000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1862000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>824000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1899000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1492000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1004000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1430000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1177000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>933000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3882000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4060000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3927000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3701000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3280000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3342000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3263000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3258000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3011000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2791000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3198000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2845000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2361000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2525000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2499000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2275000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2631000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2379000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2414000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2066000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1828000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1513000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1420000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1693000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2073000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2108000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2048000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1862000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>824000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1899000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1569000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1492000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1004000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1177000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>933000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3148,8 +3209,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -3166,36 +3227,36 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>27000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>75000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-777000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E32" s="3">
         <v>143000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-26000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-80000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>106000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>67000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-104000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-209000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-243000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-215000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>85000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>155000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-140000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>58000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-173000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>22000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3882000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4060000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3927000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3701000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3280000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3342000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3263000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3258000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3011000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2791000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3198000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2845000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2361000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2525000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2499000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2275000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2631000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2379000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2414000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2066000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1828000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1513000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1420000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1693000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2100000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2108000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2048000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1862000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>899000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1899000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1569000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1492000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>227000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1177000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>933000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3882000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4060000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3927000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3701000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3280000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3342000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3263000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3258000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3011000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2791000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3198000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2845000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2361000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2525000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2499000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2275000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2631000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2379000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2414000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2066000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1828000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1513000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1420000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1693000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2100000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2108000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2048000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1862000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>899000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1899000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1569000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1492000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>227000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1177000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>933000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,365 +4218,375 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7906000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10566000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10313000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9031000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7575000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8442000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11063000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6996000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7293000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8588000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6890000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6170000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6566000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7008000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7633000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5921000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6879000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7421000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6406000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6216000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7246000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10113000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10225000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11137000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10207000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6988000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5101000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5691000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5857000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6682000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6871000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6210000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6890000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5933000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5559000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6006000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6721000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5205000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E42" s="3">
         <v>332000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>335000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>336000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>319000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>330000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>338000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>362000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>364000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>592000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>602000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>344000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>402000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>400000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>412000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>438000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>449000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>473000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>510000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>544000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>489000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>483000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>400000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>390000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>477000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>688000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>751000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>809000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1317000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1696000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1622000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1535000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1378000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1849000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1864000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1782000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1654000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1614000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1774000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4720000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4609000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4247000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4184000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3965000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3773000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4014000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4195000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4231000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4060000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3925000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3763000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3511000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4813000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4264000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4315000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4138000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4459000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3765000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3785000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4398000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4411000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3775000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3971000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3657000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5557000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5274000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4207000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4047000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4728000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3612000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3696000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3653000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3344000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3057000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2979000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2638000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2509000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2435000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,603 +4704,621 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9008000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7490000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7850000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8047000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7438000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6687000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6885000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6227000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6536000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5689000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5566000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5655000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5345000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4385000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4514000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4537000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4487000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4596000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4701000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4534000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4272000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4106000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4069000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3883000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3782000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3669000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3721000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3458000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3175000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3065000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2959000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2864000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2786000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2751000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2604000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2587000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2384000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2362000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22498000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23558000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23223000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22140000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19804000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19724000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22300000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17780000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18424000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18961000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16983000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16530000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16420000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16606000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16823000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15211000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15953000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16949000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15382000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15079000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16405000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19113000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18469000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19381000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18123000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16902000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14847000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14165000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14396000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16171000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15064000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14305000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14707000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13797000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13231000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>12885000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>13228000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>11776000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1677000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1705000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1685000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1638000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1598000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1607000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1601000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1709000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1737000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1729000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1650000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1664000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1503000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2805000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2694000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2745000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2986000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2966000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2658000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2479000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2133000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1970000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1613000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1621000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1509000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1526000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1296000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1276000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>722000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>635000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>480000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>441000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>409000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>427000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>388000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>392000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>298000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>307000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>321000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2349000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2303000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2299000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2225000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2171000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2138000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2176000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2148000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2077000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2061000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1972000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1986000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>2006000</v>
       </c>
       <c r="P48" s="3">
         <v>2006000</v>
       </c>
       <c r="Q48" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="R48" s="3">
         <v>1951000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1950000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1957000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1907000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1860000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1839000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1850000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1902000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1887000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1872000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1901000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1828000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1492000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1348000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1305000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>921000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>876000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>860000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>839000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>829000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>901000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>845000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>748000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>733000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>698000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15020000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15114000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15165000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15227000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14885000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14646000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11956000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11712000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11668000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11746000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11510000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11628000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11602000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11381000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10758000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11195000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11300000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11333000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11130000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11274000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10372000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6713000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5666000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5561000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5517000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5438000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5034000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4756000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3969000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3895000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3973000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4017000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4222000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4155000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4162000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2477000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2478000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2561000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2065000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2040000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1674000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1836000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1863000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1802000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1560000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1602000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1473000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1426000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1272000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1297000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1423000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5926000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5386000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5130000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4967000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4514000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4380000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4240000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4040000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3886000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3959000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3692000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3598000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3542000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3312000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3186000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3128000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3238000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2947000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2848000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2767000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2121000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2232000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2175000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2162000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1929000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1967000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52449000</v>
+      </c>
+      <c r="E54" s="3">
         <v>54157000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53289000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51431000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48470000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>48081000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>47237000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42333000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42602000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42448000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39674000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>39004000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38936000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38724000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37612000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>36231000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37163000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37669000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35410000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34911000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34800000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33584000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>31594000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32127000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30648000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>29236000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25981000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>24731000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23520000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24860000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23340000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22471000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22944000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>21329000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>20914000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>19839000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>18570000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>18675000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>17323000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,136 +6014,140 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1030000</v>
+      </c>
+      <c r="E57" s="3">
         <v>999000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>935000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>818000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>993000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>929000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>911000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>835000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>790000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>834000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>589000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>643000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>735000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>926000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>615000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>633000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>666000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>738000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>557000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>547000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>476000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>527000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>341000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>369000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>371000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>489000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>505000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>432000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>508000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>537000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>382000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>345000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>370000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>933000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>722000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>654000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>680000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>609000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1748000</v>
+      </c>
+      <c r="E58" s="3">
         <v>906000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -6021,49 +6155,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>883000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>750000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1086000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2086000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1479000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1337000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1336000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>276000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>274000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>957000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>735000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>778000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>792000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>650000</v>
-      </c>
-      <c r="V58" s="3">
-        <v>649000</v>
       </c>
       <c r="W58" s="3">
         <v>649000</v>
@@ -6071,8 +6205,8 @@
       <c r="X58" s="3">
         <v>649000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
+      <c r="Y58" s="3">
+        <v>649000</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
@@ -6080,8 +6214,8 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -6090,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>500000</v>
@@ -6098,8 +6232,8 @@
       <c r="AG58" s="3">
         <v>500000</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
+      <c r="AH58" s="3">
+        <v>500000</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>5</v>
@@ -6113,8 +6247,8 @@
       <c r="AL58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM58" s="3">
-        <v>0</v>
+      <c r="AM58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AN58" s="3">
         <v>0</v>
@@ -6122,484 +6256,499 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8985000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8499000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8492000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8587000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8309000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7469000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6882000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5979000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6609000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5920000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5373000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5989000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5918000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12971000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11904000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10717000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10484000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11632000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10354000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10101000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10350000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10671000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9617000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9554000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9341000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11415000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10209000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9065000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9238000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10556000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8827000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9110000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8578000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7860000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7262000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6929000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>6415000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6597000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>6684000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22934000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22762000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20693000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19029000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17828000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19220000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17294000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15594000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16905000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16264000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14519000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14636000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13651000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14171000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13476000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12085000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11928000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13162000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11561000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11297000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11475000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11847000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9958000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9923000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9712000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11904000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10714000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9497000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10246000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11593000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9709000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9455000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8948000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8793000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7984000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7583000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7095000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>7206000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>7121000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17212000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18927000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18983000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18970000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18802000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18103000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17608000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14519000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13543000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14977000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14229000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14284000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15292000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13749000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13577000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13746000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13868000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13109000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13211000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13250000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13221000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12023000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12574000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12498000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12466000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8527000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7735000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7806000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5799000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5834000</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>5858000</v>
       </c>
       <c r="AH61" s="3">
         <v>5858000</v>
       </c>
       <c r="AI61" s="3">
+        <v>5858000</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>6469000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5424000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5393000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5326000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5216000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5180000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3326000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4801000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3991000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4990000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4799000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4365000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3477000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4102000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4068000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4155000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3523000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3860000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3820000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3931000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4427000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4116000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4138000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4237000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3986000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3836000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3795000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3651000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3197000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3181000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3158000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2972000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2814000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2483000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2319000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2212000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1944000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1906000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1725000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1544000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>999000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>982000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>621000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>605000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>627000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45727000</v>
+      </c>
+      <c r="E66" s="3">
         <v>46411000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45370000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43557000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41774000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41566000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39739000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34851000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35294000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35451000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33293000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33425000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33529000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32426000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31251000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30060000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30129000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30357000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28707000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28469000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28473000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>27193000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25798000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>25657000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>25250000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23343000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21032000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19723000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>18352000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19465000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17565000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17214000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17241000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>15861000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14472000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13987000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12959000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>13019000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>88146000</v>
+      </c>
+      <c r="E72" s="3">
         <v>85035000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>81752000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>78509000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>75495000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>72907000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>70258000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>67604000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>64959000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>62564000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>60390000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57730000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55424000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53607000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>51625000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>49599000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47800000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>45648000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>43750000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>41771000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>40140000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38747000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37403000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36288000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35273000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33984000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>32289000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>30517000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>28806000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>27283000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>26726000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>25086000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>23852000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22364000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>22401000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>21205000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>20263000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>19418000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>18722000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6719000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7737000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7904000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7853000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6671000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6485000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7440000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7421000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7243000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6929000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6311000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5504000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5330000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6298000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6361000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6171000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7034000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7312000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6703000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6442000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6327000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6391000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5796000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6470000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5398000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5893000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4949000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5008000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5168000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5395000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5775000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5257000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5703000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5468000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6442000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5852000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5611000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5656000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6219000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3882000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4060000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3927000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3701000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3280000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3342000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3263000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3258000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3011000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2791000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3198000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2845000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2361000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2525000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2499000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2275000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2631000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2379000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2414000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2066000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1828000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1513000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1420000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1693000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2100000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2108000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2048000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1862000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>899000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1899000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1569000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1492000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>227000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1177000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>933000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1184000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E83" s="3">
         <v>376000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>225000</v>
       </c>
       <c r="F83" s="3">
         <v>225000</v>
       </c>
       <c r="G83" s="3">
+        <v>225000</v>
+      </c>
+      <c r="H83" s="3">
         <v>216000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>346000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>211000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>192000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>191000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>321000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>185000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>189000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>192000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>184000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>185000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>189000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>192000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>189000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>188000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>186000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>163000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>150000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>141000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>145000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>144000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>146000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>137000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>122000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>117000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>113000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>111000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>115000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>120000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>116000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>118000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>111000</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>92000</v>
       </c>
       <c r="AN83" s="3">
         <v>92000</v>
       </c>
       <c r="AO83" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AP83" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2999000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5002000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5663000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4603000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2380000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4834000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5136000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3138000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1672000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4130000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3233000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2698000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1919000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3100000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3856000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2457000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1782000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3189000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2543000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2268000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1463000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2253000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1654000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1458000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1859000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2980000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1536000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1312000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1332000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2367000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1489000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1035000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1823000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1789000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>745000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>992000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1424000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-112000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-178000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-40000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-159000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-95000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-107000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-115000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-157000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-77000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-104000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-80000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-110000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-339000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-277000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-187000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-294000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-228000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-249000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-81000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-65000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-79000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-131000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-116000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-132000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-90000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-204000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-198000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-362000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-421000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-374000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-227000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-340000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2678000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-256000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-294000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-174000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-214000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-522000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-218000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-397000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-350000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-308000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-525000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-287000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-438000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-132000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1142000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3560000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1054000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-199000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-119000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-507000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-460000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-626000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>213000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>367000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1122000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,61 +10221,62 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>777000</v>
+      </c>
+      <c r="E96" s="3">
         <v>684000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>687000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>691000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>694000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>606000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>611000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>615000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>616000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>534000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>538000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>541000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>545000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-473000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-474000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-477000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-479000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-434000</v>
       </c>
       <c r="U96" s="3">
         <v>-434000</v>
@@ -10051,64 +10285,67 @@
         <v>-434000</v>
       </c>
       <c r="W96" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-439000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-399000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-402000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-401000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-403000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-333000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-335000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-337000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-340000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-259000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-263000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-235000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-236000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-209000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5005000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4186000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4000000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3006000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2987000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4041000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-857000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3257000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2350000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2779000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1955000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3614000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1739000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2137000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2195000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-606000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1375000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2468000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-409000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2100000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-582000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2125000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-937000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2223000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1751000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>675000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-774000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-274000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>142000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>28000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-95000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>157000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-86000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>20000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>37000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>284000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-185000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-174000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-28000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>284000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-185000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-174000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-28000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-73000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-56000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>77000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-101000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>191000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>115000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>39000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-88000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>59000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-77000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>28000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-54000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-71000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>95000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>71000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>88000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>35000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-109000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2484000</v>
+      </c>
+      <c r="E102" s="3">
         <v>403000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1273000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1590000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-826000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2159000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4165000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-385000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1278000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1723000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>221000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-279000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-396000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-580000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1624000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1063000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-687000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1061000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>218000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-992000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2804000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>15000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-898000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>969000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3364000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1997000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-473000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-140000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-752000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-141000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>710000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-656000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>832000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>401000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>440000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-598000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1516000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>29000</v>
       </c>
     </row>
